--- a/data/fmsForecastOutput/File1/RPT_RPT7432825158817CT_fmsForecastOutput.xlsx
+++ b/data/fmsForecastOutput/File1/RPT_RPT7432825158817CT_fmsForecastOutput.xlsx
@@ -1875,49 +1875,49 @@
         </is>
       </c>
       <c r="C8" s="148" t="n">
-        <v>245.8826609986716</v>
+        <v>508.5550443451468</v>
       </c>
       <c r="D8" s="149" t="n">
-        <v>270.3380899851418</v>
+        <v>567.3314110269247</v>
       </c>
       <c r="E8" s="149" t="n">
-        <v>296.6761486807944</v>
+        <v>628.5549286153198</v>
       </c>
       <c r="F8" s="149" t="n">
-        <v>323.6944370668982</v>
+        <v>694.8829897053398</v>
       </c>
       <c r="G8" s="150" t="n">
-        <v>348.6721921705754</v>
+        <v>752.7479013350373</v>
       </c>
       <c r="H8" s="148" t="n">
-        <v>37.09946383014144</v>
+        <v>76.7322079429614</v>
       </c>
       <c r="I8" s="149" t="n">
-        <v>42.25355911349474</v>
+        <v>88.6733028042259</v>
       </c>
       <c r="J8" s="149" t="n">
-        <v>46.92306984755228</v>
+        <v>99.41387924033405</v>
       </c>
       <c r="K8" s="149" t="n">
-        <v>53.48188141829421</v>
+        <v>114.8109000320265</v>
       </c>
       <c r="L8" s="150" t="n">
-        <v>58.51947333720744</v>
+        <v>126.3376080196969</v>
       </c>
       <c r="M8" s="151" t="n">
-        <v>9538896.079221018</v>
+        <v>19729141.12312376</v>
       </c>
       <c r="N8" s="152" t="n">
-        <v>11170719.1322164</v>
+        <v>23442866.84800545</v>
       </c>
       <c r="O8" s="152" t="n">
-        <v>12639565.28023382</v>
+        <v>26778900.45348411</v>
       </c>
       <c r="P8" s="152" t="n">
-        <v>14586124.87895032</v>
+        <v>31312401.1519719</v>
       </c>
       <c r="Q8" s="153" t="n">
-        <v>16205988.39904837</v>
+        <v>34987085.37810691</v>
       </c>
       <c r="S8" s="21" t="inlineStr">
         <is>
@@ -1925,49 +1925,49 @@
         </is>
       </c>
       <c r="T8" s="148" t="n">
-        <v>343.4416067561589</v>
+        <v>710.3345996194113</v>
       </c>
       <c r="U8" s="149" t="n">
-        <v>377.6002244924043</v>
+        <v>792.4316849953827</v>
       </c>
       <c r="V8" s="149" t="n">
-        <v>414.3884435580905</v>
+        <v>877.9468781628096</v>
       </c>
       <c r="W8" s="149" t="n">
-        <v>452.1267872763362</v>
+        <v>970.591946266657</v>
       </c>
       <c r="X8" s="150" t="n">
-        <v>487.0149746382547</v>
+        <v>1051.415938264262</v>
       </c>
       <c r="Y8" s="148" t="n">
-        <v>46.9051935770975</v>
+        <v>97.01323673143176</v>
       </c>
       <c r="Z8" s="149" t="n">
-        <v>53.45389816329041</v>
+        <v>112.1783299998008</v>
       </c>
       <c r="AA8" s="149" t="n">
-        <v>59.37354250509095</v>
+        <v>125.7921573300442</v>
       </c>
       <c r="AB8" s="149" t="n">
-        <v>67.72610700365402</v>
+        <v>145.3893373709001</v>
       </c>
       <c r="AC8" s="150" t="n">
-        <v>74.12705611135368</v>
+        <v>160.0327963426128</v>
       </c>
       <c r="AD8" s="151" t="n">
-        <v>9538896.079221018</v>
+        <v>19729141.12312376</v>
       </c>
       <c r="AE8" s="152" t="n">
-        <v>11170719.1322164</v>
+        <v>23442866.84800545</v>
       </c>
       <c r="AF8" s="152" t="n">
-        <v>12639565.28023382</v>
+        <v>26778900.45348411</v>
       </c>
       <c r="AG8" s="152" t="n">
-        <v>14586124.87895032</v>
+        <v>31312401.1519719</v>
       </c>
       <c r="AH8" s="153" t="n">
-        <v>16205988.39904837</v>
+        <v>34987085.37810691</v>
       </c>
       <c r="AQ8" s="28" t="inlineStr">
         <is>
@@ -1980,34 +1980,34 @@
         </is>
       </c>
       <c r="AS8" s="154" t="n">
-        <v>0.985</v>
+        <v>1.985</v>
       </c>
       <c r="AT8" s="154" t="n">
-        <v>0.98</v>
+        <v>1.98</v>
       </c>
       <c r="AU8" s="154" t="n">
-        <v>0.975</v>
+        <v>1.975</v>
       </c>
       <c r="AV8" s="154" t="n">
-        <v>0.97</v>
+        <v>1.97</v>
       </c>
       <c r="AW8" s="154" t="n">
-        <v>0.965</v>
+        <v>1.965</v>
       </c>
       <c r="AX8" s="154" t="n">
-        <v>0.97</v>
+        <v>1.97</v>
       </c>
       <c r="AY8" s="154" t="n">
-        <v>0.9675</v>
+        <v>1.9675</v>
       </c>
       <c r="AZ8" s="154" t="n">
-        <v>0.965</v>
+        <v>1.965</v>
       </c>
       <c r="BA8" s="154" t="n">
-        <v>0.9625</v>
+        <v>1.9625</v>
       </c>
       <c r="BB8" s="154" t="n">
-        <v>0.96</v>
+        <v>1.96</v>
       </c>
       <c r="BD8" s="31" t="inlineStr">
         <is>
@@ -2022,49 +2022,49 @@
         </is>
       </c>
       <c r="C9" s="155" t="n">
-        <v>650.6504866467475</v>
+        <v>1349.98054145868</v>
       </c>
       <c r="D9" s="156" t="n">
-        <v>700.4583929468304</v>
+        <v>1475.570375901053</v>
       </c>
       <c r="E9" s="156" t="n">
-        <v>753.2311592282185</v>
+        <v>1602.840321167589</v>
       </c>
       <c r="F9" s="156" t="n">
-        <v>798.8860516383605</v>
+        <v>1723.046238328242</v>
       </c>
       <c r="G9" s="157" t="n">
-        <v>842.0000221873739</v>
+        <v>1827.692425874185</v>
       </c>
       <c r="H9" s="155" t="n">
-        <v>20.75800285863988</v>
+        <v>43.06905245415077</v>
       </c>
       <c r="I9" s="156" t="n">
-        <v>24.12293199755972</v>
+        <v>50.81684250470056</v>
       </c>
       <c r="J9" s="156" t="n">
-        <v>27.66756061956131</v>
+        <v>58.87526187156173</v>
       </c>
       <c r="K9" s="156" t="n">
-        <v>32.25690910457772</v>
+        <v>69.5720569645127</v>
       </c>
       <c r="L9" s="157" t="n">
-        <v>36.37825922566282</v>
+        <v>78.96468776866101</v>
       </c>
       <c r="M9" s="158" t="n">
-        <v>4888069.967885035</v>
+        <v>10141849.54497081</v>
       </c>
       <c r="N9" s="159" t="n">
-        <v>5839563.396704018</v>
+        <v>12301496.90993373</v>
       </c>
       <c r="O9" s="159" t="n">
-        <v>6816666.058827665</v>
+        <v>14505543.32645857</v>
       </c>
       <c r="P9" s="159" t="n">
-        <v>8008723.280544685</v>
+        <v>17273302.61187367</v>
       </c>
       <c r="Q9" s="160" t="n">
-        <v>9107005.630963491</v>
+        <v>19768176.69299477</v>
       </c>
       <c r="S9" s="32" t="inlineStr">
         <is>
@@ -2072,49 +2072,49 @@
         </is>
       </c>
       <c r="T9" s="155" t="n">
-        <v>764.0780720320506</v>
+        <v>1585.321997858661</v>
       </c>
       <c r="U9" s="156" t="n">
-        <v>822.5689666041199</v>
+        <v>1732.805847539776</v>
       </c>
       <c r="V9" s="156" t="n">
-        <v>884.5415837674311</v>
+        <v>1882.262700954343</v>
       </c>
       <c r="W9" s="156" t="n">
-        <v>938.1554715420378</v>
+        <v>2023.424057651862</v>
       </c>
       <c r="X9" s="157" t="n">
-        <v>988.7854797735109</v>
+        <v>2146.313164578818</v>
       </c>
       <c r="Y9" s="155" t="n">
-        <v>21.54580795446214</v>
+        <v>44.70360367888451</v>
       </c>
       <c r="Z9" s="156" t="n">
-        <v>25.04605985036192</v>
+        <v>52.76148350904852</v>
       </c>
       <c r="AA9" s="156" t="n">
-        <v>28.73423950043177</v>
+        <v>61.14510413585273</v>
       </c>
       <c r="AB9" s="156" t="n">
-        <v>33.51518823618823</v>
+        <v>72.285927259334</v>
       </c>
       <c r="AC9" s="157" t="n">
-        <v>37.81014062994691</v>
+        <v>82.07280977388557</v>
       </c>
       <c r="AD9" s="158" t="n">
-        <v>4888069.967885035</v>
+        <v>10141849.54497081</v>
       </c>
       <c r="AE9" s="159" t="n">
-        <v>5839563.396704018</v>
+        <v>12301496.90993373</v>
       </c>
       <c r="AF9" s="159" t="n">
-        <v>6816666.058827665</v>
+        <v>14505543.32645857</v>
       </c>
       <c r="AG9" s="159" t="n">
-        <v>8008723.280544685</v>
+        <v>17273302.61187367</v>
       </c>
       <c r="AH9" s="160" t="n">
-        <v>9107005.630963491</v>
+        <v>19768176.69299477</v>
       </c>
       <c r="AJ9" s="39" t="n"/>
       <c r="AQ9" s="40" t="inlineStr">
@@ -2128,34 +2128,34 @@
         </is>
       </c>
       <c r="AS9" s="154" t="n">
-        <v>0.98222200886944</v>
+        <v>1.98222200886944</v>
       </c>
       <c r="AT9" s="154" t="n">
-        <v>0.959877939943838</v>
+        <v>1.95987793994383</v>
       </c>
       <c r="AU9" s="154" t="n">
-        <v>0.953844334714395</v>
+        <v>1.95384433471439</v>
       </c>
       <c r="AV9" s="154" t="n">
-        <v>0.942019789921236</v>
+        <v>1.94201978992123</v>
       </c>
       <c r="AW9" s="154" t="n">
-        <v>0.9396716375637419</v>
+        <v>1.93967163756374</v>
       </c>
       <c r="AX9" s="154" t="n">
-        <v>0.959183430955845</v>
+        <v>1.95918343095584</v>
       </c>
       <c r="AY9" s="154" t="n">
-        <v>0.958736584295856</v>
+        <v>1.95873658429585</v>
       </c>
       <c r="AZ9" s="154" t="n">
-        <v>0.957337586100609</v>
+        <v>1.9573375861006</v>
       </c>
       <c r="BA9" s="154" t="n">
-        <v>0.95373489701852</v>
+        <v>1.95373489701852</v>
       </c>
       <c r="BB9" s="154" t="n">
-        <v>0.951703088585464</v>
+        <v>1.95170308858546</v>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
@@ -2170,49 +2170,49 @@
         </is>
       </c>
       <c r="C10" s="161" t="n">
-        <v>311.5498020041764</v>
+        <v>645.0629465631996</v>
       </c>
       <c r="D10" s="162" t="n">
-        <v>342.5482281064816</v>
+        <v>719.8098238085348</v>
       </c>
       <c r="E10" s="162" t="n">
-        <v>376.6659214282824</v>
+        <v>799.2525780574081</v>
       </c>
       <c r="F10" s="162" t="n">
-        <v>410.1720905724645</v>
+        <v>881.9930784255553</v>
       </c>
       <c r="G10" s="163" t="n">
-        <v>441.8005251797445</v>
+        <v>955.6713643074301</v>
       </c>
       <c r="H10" s="161" t="n">
-        <v>29.28764490386807</v>
+        <v>60.63998242994408</v>
       </c>
       <c r="I10" s="162" t="n">
-        <v>33.5873791886085</v>
+        <v>70.57845731558544</v>
       </c>
       <c r="J10" s="162" t="n">
-        <v>37.72448948385854</v>
+        <v>80.0481109667214</v>
       </c>
       <c r="K10" s="162" t="n">
-        <v>43.36743762355332</v>
+        <v>93.25300451242795</v>
       </c>
       <c r="L10" s="163" t="n">
-        <v>48.00717341811048</v>
+        <v>103.8456912163319</v>
       </c>
       <c r="M10" s="164" t="n">
-        <v>14426966.04710605</v>
+        <v>29870990.66809458</v>
       </c>
       <c r="N10" s="165" t="n">
-        <v>17010282.52892042</v>
+        <v>35744363.75793917</v>
       </c>
       <c r="O10" s="165" t="n">
-        <v>19456231.33906149</v>
+        <v>41284443.77994268</v>
       </c>
       <c r="P10" s="165" t="n">
-        <v>22594848.15949501</v>
+        <v>48585703.76384557</v>
       </c>
       <c r="Q10" s="166" t="n">
-        <v>25312994.03001186</v>
+        <v>54755262.07110168</v>
       </c>
       <c r="S10" s="42" t="inlineStr">
         <is>
@@ -2220,49 +2220,49 @@
         </is>
       </c>
       <c r="T10" s="161" t="n">
-        <v>422.1895158958978</v>
+        <v>874.1421479967684</v>
       </c>
       <c r="U10" s="162" t="n">
-        <v>463.7148793872864</v>
+        <v>974.4219886181996</v>
       </c>
       <c r="V10" s="162" t="n">
-        <v>509.2165005236252</v>
+        <v>1080.513467450415</v>
       </c>
       <c r="W10" s="162" t="n">
-        <v>553.8250521348414</v>
+        <v>1190.890052904039</v>
       </c>
       <c r="X10" s="163" t="n">
-        <v>595.7897406975155</v>
+        <v>1288.769844945557</v>
       </c>
       <c r="Y10" s="161" t="n">
-        <v>33.53282166694908</v>
+        <v>69.42960840260945</v>
       </c>
       <c r="Z10" s="162" t="n">
-        <v>38.47335192991717</v>
+        <v>80.8455405741841</v>
       </c>
       <c r="AA10" s="162" t="n">
-        <v>43.2251585586312</v>
+        <v>91.72005602185638</v>
       </c>
       <c r="AB10" s="162" t="n">
-        <v>49.73253054097606</v>
+        <v>106.9398643103902</v>
       </c>
       <c r="AC10" s="163" t="n">
-        <v>55.08981322093075</v>
+        <v>119.1663521424491</v>
       </c>
       <c r="AD10" s="164" t="n">
-        <v>14426966.04710605</v>
+        <v>29870990.66809458</v>
       </c>
       <c r="AE10" s="165" t="n">
-        <v>17010282.52892042</v>
+        <v>35744363.75793917</v>
       </c>
       <c r="AF10" s="165" t="n">
-        <v>19456231.33906149</v>
+        <v>41284443.77994268</v>
       </c>
       <c r="AG10" s="165" t="n">
-        <v>22594848.15949501</v>
+        <v>48585703.76384557</v>
       </c>
       <c r="AH10" s="166" t="n">
-        <v>25312994.03001186</v>
+        <v>54755262.07110168</v>
       </c>
       <c r="AJ10" s="39" t="n"/>
       <c r="AQ10" s="40" t="inlineStr">
@@ -2276,34 +2276,34 @@
         </is>
       </c>
       <c r="AS10" s="154" t="n">
-        <v>0.980726167491445</v>
+        <v>1.98072616749144</v>
       </c>
       <c r="AT10" s="154" t="n">
-        <v>0.9490429845289819</v>
+        <v>1.94904298452898</v>
       </c>
       <c r="AU10" s="154" t="n">
-        <v>0.9424528226375311</v>
+        <v>1.94245282263753</v>
       </c>
       <c r="AV10" s="154" t="n">
-        <v>0.926953522955747</v>
+        <v>1.92695352295574</v>
       </c>
       <c r="AW10" s="154" t="n">
-        <v>0.926033288559604</v>
+        <v>1.9260332885596</v>
       </c>
       <c r="AX10" s="154" t="n">
-        <v>0.953359124547455</v>
+        <v>1.95335912454745</v>
       </c>
       <c r="AY10" s="154" t="n">
-        <v>0.9540178219936239</v>
+        <v>1.95401782199362</v>
       </c>
       <c r="AZ10" s="154" t="n">
-        <v>0.953211670924014</v>
+        <v>1.95321167092401</v>
       </c>
       <c r="BA10" s="154" t="n">
-        <v>0.949015226182339</v>
+        <v>1.94901522618233</v>
       </c>
       <c r="BB10" s="154" t="n">
-        <v>0.9472355209007139</v>
+        <v>1.94723552090071</v>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
@@ -2318,49 +2318,49 @@
         </is>
       </c>
       <c r="C11" s="155" t="n">
-        <v>853.6017298638247</v>
+        <v>1759.91251292705</v>
       </c>
       <c r="D11" s="156" t="n">
-        <v>940.035360088637</v>
+        <v>1965.342420571898</v>
       </c>
       <c r="E11" s="156" t="n">
-        <v>997.8078294141102</v>
+        <v>2105.353477899063</v>
       </c>
       <c r="F11" s="156" t="n">
-        <v>1051.30916834339</v>
+        <v>2249.091032043166</v>
       </c>
       <c r="G11" s="157" t="n">
-        <v>1105.370447846806</v>
+        <v>2382.791647677877</v>
       </c>
       <c r="H11" s="155" t="n">
-        <v>38.32832376178823</v>
+        <v>79.02338318673667</v>
       </c>
       <c r="I11" s="156" t="n">
-        <v>44.8667167737845</v>
+        <v>93.80334558796699</v>
       </c>
       <c r="J11" s="156" t="n">
-        <v>50.82190078951005</v>
+        <v>107.2331389135951</v>
       </c>
       <c r="K11" s="156" t="n">
-        <v>60.04852973922764</v>
+        <v>128.463266364059</v>
       </c>
       <c r="L11" s="157" t="n">
-        <v>70.49427590334128</v>
+        <v>151.9609757604638</v>
       </c>
       <c r="M11" s="158" t="n">
-        <v>143073.4632087151</v>
+        <v>294981.5696940947</v>
       </c>
       <c r="N11" s="159" t="n">
-        <v>171837.4064784538</v>
+        <v>359262.3838759826</v>
       </c>
       <c r="O11" s="159" t="n">
-        <v>197911.1861051924</v>
+        <v>417588.4290528732</v>
       </c>
       <c r="P11" s="159" t="n">
-        <v>236263.9917445437</v>
+        <v>505445.2496259495</v>
       </c>
       <c r="Q11" s="160" t="n">
-        <v>280681.8112254282</v>
+        <v>605051.7061912076</v>
       </c>
       <c r="S11" s="32" t="inlineStr">
         <is>
@@ -2368,49 +2368,49 @@
         </is>
       </c>
       <c r="T11" s="155" t="n">
-        <v>926.4162510095409</v>
+        <v>1910.037779083178</v>
       </c>
       <c r="U11" s="156" t="n">
-        <v>1020.222902135693</v>
+        <v>2132.991409830782</v>
       </c>
       <c r="V11" s="156" t="n">
-        <v>1082.92351832658</v>
+        <v>2284.945786551184</v>
       </c>
       <c r="W11" s="156" t="n">
-        <v>1140.988665222147</v>
+        <v>2440.944540279933</v>
       </c>
       <c r="X11" s="157" t="n">
-        <v>1199.66151712736</v>
+        <v>2586.05017767565</v>
       </c>
       <c r="Y11" s="155" t="n">
-        <v>39.01230915819218</v>
+        <v>80.43358939377273</v>
       </c>
       <c r="Z11" s="156" t="n">
-        <v>45.6757853639738</v>
+        <v>95.49487432078122</v>
       </c>
       <c r="AA11" s="156" t="n">
-        <v>51.74915228636099</v>
+        <v>109.1896200177056</v>
       </c>
       <c r="AB11" s="156" t="n">
-        <v>61.16874967959784</v>
+        <v>130.8597798709018</v>
       </c>
       <c r="AC11" s="157" t="n">
-        <v>71.84050886853221</v>
+        <v>154.8629826591774</v>
       </c>
       <c r="AD11" s="158" t="n">
-        <v>143073.4632087151</v>
+        <v>294981.5696940947</v>
       </c>
       <c r="AE11" s="159" t="n">
-        <v>171837.4064784538</v>
+        <v>359262.3838759826</v>
       </c>
       <c r="AF11" s="159" t="n">
-        <v>197911.1861051924</v>
+        <v>417588.4290528732</v>
       </c>
       <c r="AG11" s="159" t="n">
-        <v>236263.9917445437</v>
+        <v>505445.2496259495</v>
       </c>
       <c r="AH11" s="160" t="n">
-        <v>280681.8112254282</v>
+        <v>605051.7061912076</v>
       </c>
       <c r="AJ11" s="39" t="n"/>
       <c r="AQ11" s="40" t="inlineStr">
@@ -2424,34 +2424,34 @@
         </is>
       </c>
       <c r="AS11" s="154" t="n">
-        <v>0.985</v>
+        <v>1.985</v>
       </c>
       <c r="AT11" s="154" t="n">
-        <v>0.98</v>
+        <v>1.98</v>
       </c>
       <c r="AU11" s="154" t="n">
-        <v>0.975</v>
+        <v>1.975</v>
       </c>
       <c r="AV11" s="154" t="n">
-        <v>0.97</v>
+        <v>1.97</v>
       </c>
       <c r="AW11" s="154" t="n">
-        <v>0.965</v>
+        <v>1.965</v>
       </c>
       <c r="AX11" s="154" t="n">
-        <v>0.97</v>
+        <v>1.97</v>
       </c>
       <c r="AY11" s="154" t="n">
-        <v>0.968</v>
+        <v>1.968</v>
       </c>
       <c r="AZ11" s="154" t="n">
-        <v>0.965</v>
+        <v>1.965</v>
       </c>
       <c r="BA11" s="154" t="n">
-        <v>0.963</v>
+        <v>1.963</v>
       </c>
       <c r="BB11" s="154" t="n">
-        <v>0.96</v>
+        <v>1.96</v>
       </c>
     </row>
     <row r="12" ht="15" customHeight="1" thickTop="1">
@@ -2461,49 +2461,49 @@
         </is>
       </c>
       <c r="C12" s="161" t="n">
-        <v>313.504717764103</v>
+        <v>649.0836627994423</v>
       </c>
       <c r="D12" s="162" t="n">
-        <v>344.7396021103198</v>
+        <v>724.378002112937</v>
       </c>
       <c r="E12" s="162" t="n">
-        <v>379.041926787817</v>
+        <v>804.2487032555609</v>
       </c>
       <c r="F12" s="162" t="n">
-        <v>412.7770831439194</v>
+        <v>887.5477096223761</v>
       </c>
       <c r="G12" s="163" t="n">
-        <v>444.728419054748</v>
+        <v>961.9682994062653</v>
       </c>
       <c r="H12" s="161" t="n">
-        <v>29.35563898585155</v>
+        <v>60.77824223076616</v>
       </c>
       <c r="I12" s="162" t="n">
-        <v>33.67203751225355</v>
+        <v>70.75277429946289</v>
       </c>
       <c r="J12" s="162" t="n">
-        <v>37.82264227812011</v>
+        <v>80.25183721405345</v>
       </c>
       <c r="K12" s="162" t="n">
-        <v>43.49246542631729</v>
+        <v>93.51691179400915</v>
       </c>
       <c r="L12" s="163" t="n">
-        <v>48.17570812790436</v>
+        <v>104.2063021719951</v>
       </c>
       <c r="M12" s="164" t="n">
-        <v>14570039.51031477</v>
+        <v>30165972.23778867</v>
       </c>
       <c r="N12" s="165" t="n">
-        <v>17182119.93539887</v>
+        <v>36103626.14181516</v>
       </c>
       <c r="O12" s="165" t="n">
-        <v>19654142.52516668</v>
+        <v>41702032.20899556</v>
       </c>
       <c r="P12" s="165" t="n">
-        <v>22831112.15123956</v>
+        <v>49091149.01347151</v>
       </c>
       <c r="Q12" s="166" t="n">
-        <v>25593675.84123729</v>
+        <v>55360313.77729289</v>
       </c>
       <c r="S12" s="42" t="inlineStr">
         <is>
@@ -2511,49 +2511,49 @@
         </is>
       </c>
       <c r="T12" s="161" t="n">
-        <v>424.4580895263711</v>
+        <v>878.8027606714917</v>
       </c>
       <c r="U12" s="162" t="n">
-        <v>466.2584514205111</v>
+        <v>979.717338654291</v>
       </c>
       <c r="V12" s="162" t="n">
-        <v>511.947578565457</v>
+        <v>1086.247053684318</v>
       </c>
       <c r="W12" s="162" t="n">
-        <v>556.7901553918311</v>
+        <v>1197.202672673585</v>
       </c>
       <c r="X12" s="163" t="n">
-        <v>599.0969732591585</v>
+        <v>1295.874677337872</v>
       </c>
       <c r="Y12" s="161" t="n">
-        <v>33.57913501177395</v>
+        <v>69.5226154889299</v>
       </c>
       <c r="Z12" s="162" t="n">
-        <v>38.53412058782081</v>
+        <v>80.96914051566414</v>
       </c>
       <c r="AA12" s="162" t="n">
-        <v>43.29697330978946</v>
+        <v>91.86723731166937</v>
       </c>
       <c r="AB12" s="162" t="n">
-        <v>49.82893673885562</v>
+        <v>107.1415068361967</v>
       </c>
       <c r="AC12" s="163" t="n">
-        <v>55.23104365794649</v>
+        <v>119.467321775826</v>
       </c>
       <c r="AD12" s="164" t="n">
-        <v>14570039.51031477</v>
+        <v>30165972.23778867</v>
       </c>
       <c r="AE12" s="165" t="n">
-        <v>17182119.93539887</v>
+        <v>36103626.14181516</v>
       </c>
       <c r="AF12" s="165" t="n">
-        <v>19654142.52516668</v>
+        <v>41702032.20899556</v>
       </c>
       <c r="AG12" s="165" t="n">
-        <v>22831112.15123956</v>
+        <v>49091149.01347151</v>
       </c>
       <c r="AH12" s="166" t="n">
-        <v>25593675.84123729</v>
+        <v>55360313.77729289</v>
       </c>
       <c r="AQ12" s="40" t="inlineStr">
         <is>
@@ -2566,34 +2566,34 @@
         </is>
       </c>
       <c r="AS12" s="154" t="n">
-        <v>0.9822</v>
+        <v>1.9822</v>
       </c>
       <c r="AT12" s="154" t="n">
-        <v>0.9599</v>
+        <v>1.9599</v>
       </c>
       <c r="AU12" s="154" t="n">
-        <v>0.9538</v>
+        <v>1.9538</v>
       </c>
       <c r="AV12" s="154" t="n">
-        <v>0.9419999999999999</v>
+        <v>1.942</v>
       </c>
       <c r="AW12" s="154" t="n">
-        <v>0.9397</v>
+        <v>1.9397</v>
       </c>
       <c r="AX12" s="154" t="n">
-        <v>0.9592000000000001</v>
+        <v>1.9592</v>
       </c>
       <c r="AY12" s="154" t="n">
-        <v>0.9587</v>
+        <v>1.9587</v>
       </c>
       <c r="AZ12" s="154" t="n">
-        <v>0.9573</v>
+        <v>1.9573</v>
       </c>
       <c r="BA12" s="154" t="n">
-        <v>0.9537</v>
+        <v>1.9537</v>
       </c>
       <c r="BB12" s="154" t="n">
-        <v>0.9517</v>
+        <v>1.9517</v>
       </c>
     </row>
     <row r="13" ht="15" customHeight="1" thickBot="1">
@@ -2603,49 +2603,49 @@
         </is>
       </c>
       <c r="C13" s="155" t="n">
-        <v>3805.200098079478</v>
+        <v>7724.634122656296</v>
       </c>
       <c r="D13" s="156" t="n">
-        <v>4145.287101500088</v>
+        <v>8514.989319490187</v>
       </c>
       <c r="E13" s="156" t="n">
-        <v>4247.998455488951</v>
+        <v>8831.553014418549</v>
       </c>
       <c r="F13" s="156" t="n">
-        <v>4651.363530807002</v>
+        <v>9812.100488731105</v>
       </c>
       <c r="G13" s="157" t="n">
-        <v>5074.819930847304</v>
+        <v>10800.16338190327</v>
       </c>
       <c r="H13" s="155" t="n">
-        <v>3790.9693894778</v>
+        <v>7695.745492775944</v>
       </c>
       <c r="I13" s="156" t="n">
-        <v>4126.531525489154</v>
+        <v>8476.462789118819</v>
       </c>
       <c r="J13" s="156" t="n">
-        <v>3951.72312617023</v>
+        <v>8215.599099849285</v>
       </c>
       <c r="K13" s="156" t="n">
-        <v>4265.64333278015</v>
+        <v>8998.419657614446</v>
       </c>
       <c r="L13" s="157" t="n">
-        <v>4665.144903435879</v>
+        <v>9928.298509883987</v>
       </c>
       <c r="M13" s="158" t="n">
-        <v>1898653.394745209</v>
+        <v>3854305.272289974</v>
       </c>
       <c r="N13" s="159" t="n">
-        <v>2205194.566085305</v>
+        <v>4529772.65936999</v>
       </c>
       <c r="O13" s="159" t="n">
-        <v>2364673.018946981</v>
+        <v>4916135.292283592</v>
       </c>
       <c r="P13" s="159" t="n">
-        <v>2738987.489065457</v>
+        <v>5777923.033125032</v>
       </c>
       <c r="Q13" s="160" t="n">
-        <v>3230542.39303522</v>
+        <v>6875196.781833353</v>
       </c>
       <c r="S13" s="32" t="inlineStr">
         <is>
@@ -2653,49 +2653,49 @@
         </is>
       </c>
       <c r="T13" s="155" t="n">
-        <v>3110.155067973367</v>
+        <v>6313.678478286868</v>
       </c>
       <c r="U13" s="156" t="n">
-        <v>3388.122925110323</v>
+        <v>6959.670057592425</v>
       </c>
       <c r="V13" s="156" t="n">
-        <v>3472.07336921656</v>
+        <v>7218.411294515744</v>
       </c>
       <c r="W13" s="156" t="n">
-        <v>3801.761138823491</v>
+        <v>8019.855270657989</v>
       </c>
       <c r="X13" s="157" t="n">
-        <v>4147.870419467054</v>
+        <v>8827.44192457057</v>
       </c>
       <c r="Y13" s="155" t="n">
-        <v>3100.641741933631</v>
+        <v>6294.366231610647</v>
       </c>
       <c r="Z13" s="156" t="n">
-        <v>3375.582895546293</v>
+        <v>6933.911113714891</v>
       </c>
       <c r="AA13" s="156" t="n">
-        <v>3271.592590513332</v>
+        <v>6801.613443941742</v>
       </c>
       <c r="AB13" s="156" t="n">
-        <v>3540.117566446097</v>
+        <v>7467.915391653916</v>
       </c>
       <c r="AC13" s="157" t="n">
-        <v>3870.090995076567</v>
+        <v>8236.2754973024</v>
       </c>
       <c r="AD13" s="158" t="n">
-        <v>1898653.394745209</v>
+        <v>3854305.272289974</v>
       </c>
       <c r="AE13" s="159" t="n">
-        <v>2205194.566085305</v>
+        <v>4529772.65936999</v>
       </c>
       <c r="AF13" s="159" t="n">
-        <v>2364673.018946981</v>
+        <v>4916135.292283592</v>
       </c>
       <c r="AG13" s="159" t="n">
-        <v>2738987.489065457</v>
+        <v>5777923.033125032</v>
       </c>
       <c r="AH13" s="160" t="n">
-        <v>3230542.39303522</v>
+        <v>6875196.781833353</v>
       </c>
       <c r="AJ13" s="39" t="n"/>
       <c r="AQ13" s="49" t="inlineStr">
@@ -2709,34 +2709,34 @@
         </is>
       </c>
       <c r="AS13" s="154" t="n">
-        <v>0.9657</v>
+        <v>1.9657</v>
       </c>
       <c r="AT13" s="154" t="n">
-        <v>0.9340000000000001</v>
+        <v>1.934</v>
       </c>
       <c r="AU13" s="154" t="n">
-        <v>0.9275</v>
+        <v>1.9275</v>
       </c>
       <c r="AV13" s="154" t="n">
-        <v>0.912</v>
+        <v>1.912</v>
       </c>
       <c r="AW13" s="154" t="n">
-        <v>0.911</v>
+        <v>1.911</v>
       </c>
       <c r="AX13" s="154" t="n">
-        <v>0.9384</v>
+        <v>1.9384</v>
       </c>
       <c r="AY13" s="154" t="n">
-        <v>0.9389999999999999</v>
+        <v>1.939</v>
       </c>
       <c r="AZ13" s="154" t="n">
-        <v>0.9382</v>
+        <v>1.9382</v>
       </c>
       <c r="BA13" s="154" t="n">
-        <v>0.9340000000000001</v>
+        <v>1.934</v>
       </c>
       <c r="BB13" s="154" t="n">
-        <v>0.9322</v>
+        <v>1.9322</v>
       </c>
     </row>
     <row r="14" ht="15.6" customHeight="1" thickBot="1" thickTop="1">
@@ -2746,49 +2746,49 @@
         </is>
       </c>
       <c r="C14" s="167" t="n">
-        <v>350.5941392948162</v>
+        <v>724.2414428987361</v>
       </c>
       <c r="D14" s="168" t="n">
-        <v>384.8763347858917</v>
+        <v>806.6529069457438</v>
       </c>
       <c r="E14" s="168" t="n">
-        <v>420.1357219241933</v>
+        <v>889.5100382985331</v>
       </c>
       <c r="F14" s="168" t="n">
-        <v>457.4269465660445</v>
+        <v>981.5601988357204</v>
       </c>
       <c r="G14" s="169" t="n">
-        <v>495.3841975152901</v>
+        <v>1069.603629999898</v>
       </c>
       <c r="H14" s="167" t="n">
-        <v>33.14758724584033</v>
+        <v>68.47477959507951</v>
       </c>
       <c r="I14" s="168" t="n">
-        <v>37.95384020239866</v>
+        <v>79.54652640841294</v>
       </c>
       <c r="J14" s="168" t="n">
-        <v>42.32450561604991</v>
+        <v>89.60931110326301</v>
       </c>
       <c r="K14" s="168" t="n">
-        <v>48.65063146587014</v>
+        <v>104.3959562365399</v>
       </c>
       <c r="L14" s="169" t="n">
-        <v>54.18601986500762</v>
+        <v>116.9951803742586</v>
       </c>
       <c r="M14" s="170" t="n">
-        <v>16468692.90505998</v>
+        <v>34020277.51007865</v>
       </c>
       <c r="N14" s="171" t="n">
-        <v>19387314.50148418</v>
+        <v>40633398.80118515</v>
       </c>
       <c r="O14" s="171" t="n">
-        <v>22018815.54411366</v>
+        <v>46618167.50127914</v>
       </c>
       <c r="P14" s="171" t="n">
-        <v>25570099.64030501</v>
+        <v>54869072.04659656</v>
       </c>
       <c r="Q14" s="172" t="n">
-        <v>28824218.23427251</v>
+        <v>62235510.55912625</v>
       </c>
       <c r="S14" s="51" t="inlineStr">
         <is>
@@ -2796,49 +2796,49 @@
         </is>
       </c>
       <c r="T14" s="167" t="n">
-        <v>471.3868387539158</v>
+        <v>973.7695129453571</v>
       </c>
       <c r="U14" s="168" t="n">
-        <v>516.968528774744</v>
+        <v>1083.501709107676</v>
       </c>
       <c r="V14" s="168" t="n">
-        <v>563.5448716067365</v>
+        <v>1193.135442113864</v>
       </c>
       <c r="W14" s="168" t="n">
-        <v>612.8195926529052</v>
+        <v>1315.006310254531</v>
       </c>
       <c r="X14" s="169" t="n">
-        <v>662.6368851858588</v>
+        <v>1430.725528431383</v>
       </c>
       <c r="Y14" s="167" t="n">
-        <v>37.9014165574151</v>
+        <v>78.29502418568872</v>
       </c>
       <c r="Z14" s="168" t="n">
-        <v>43.41607340593966</v>
+        <v>90.99468752879739</v>
       </c>
       <c r="AA14" s="168" t="n">
-        <v>48.42910334268923</v>
+        <v>102.5339463443479</v>
       </c>
       <c r="AB14" s="168" t="n">
-        <v>55.71270456749253</v>
+        <v>119.5499604548288</v>
       </c>
       <c r="AC14" s="169" t="n">
-        <v>62.09069160254664</v>
+        <v>134.0624700190164</v>
       </c>
       <c r="AD14" s="170" t="n">
-        <v>16468692.90505998</v>
+        <v>34020277.51007865</v>
       </c>
       <c r="AE14" s="171" t="n">
-        <v>19387314.50148418</v>
+        <v>40633398.80118515</v>
       </c>
       <c r="AF14" s="171" t="n">
-        <v>22018815.54411366</v>
+        <v>46618167.50127914</v>
       </c>
       <c r="AG14" s="171" t="n">
-        <v>25570099.64030501</v>
+        <v>54869072.04659656</v>
       </c>
       <c r="AH14" s="172" t="n">
-        <v>28824218.23427251</v>
+        <v>62235510.55912625</v>
       </c>
       <c r="AR14" s="58" t="inlineStr">
         <is>
@@ -3666,34 +3666,34 @@
         </is>
       </c>
       <c r="AS22" s="178" t="n">
-        <v>0.97097200886944</v>
+        <v>1.97097200886944</v>
       </c>
       <c r="AT22" s="178" t="n">
-        <v>0.948627939943838</v>
+        <v>1.94862793994383</v>
       </c>
       <c r="AU22" s="178" t="n">
-        <v>0.942594334714395</v>
+        <v>1.94259433471439</v>
       </c>
       <c r="AV22" s="178" t="n">
-        <v>0.930769789921236</v>
+        <v>1.93076978992123</v>
       </c>
       <c r="AW22" s="178" t="n">
-        <v>0.928421637563742</v>
+        <v>1.92842163756374</v>
       </c>
       <c r="AX22" s="178" t="n">
-        <v>0.947933430955845</v>
+        <v>1.94793343095584</v>
       </c>
       <c r="AY22" s="178" t="n">
-        <v>0.947486584295856</v>
+        <v>1.94748658429585</v>
       </c>
       <c r="AZ22" s="178" t="n">
-        <v>0.9460875861006091</v>
+        <v>1.9460875861006</v>
       </c>
       <c r="BA22" s="178" t="n">
-        <v>0.94248489701852</v>
+        <v>1.94248489701852</v>
       </c>
       <c r="BB22" s="178" t="n">
-        <v>0.9404530885854641</v>
+        <v>1.94045308858546</v>
       </c>
     </row>
     <row r="23" ht="15.6" customHeight="1" thickBot="1" thickTop="1">
@@ -3803,34 +3803,34 @@
         </is>
       </c>
       <c r="AS23" s="178" t="n">
-        <v>0.97095</v>
+        <v>1.97095</v>
       </c>
       <c r="AT23" s="178" t="n">
-        <v>0.94865</v>
+        <v>1.94865</v>
       </c>
       <c r="AU23" s="178" t="n">
-        <v>0.94255</v>
+        <v>1.94255</v>
       </c>
       <c r="AV23" s="178" t="n">
-        <v>0.93075</v>
+        <v>1.93075</v>
       </c>
       <c r="AW23" s="178" t="n">
-        <v>0.92845</v>
+        <v>1.92845</v>
       </c>
       <c r="AX23" s="178" t="n">
-        <v>0.9479500000000001</v>
+        <v>1.94795</v>
       </c>
       <c r="AY23" s="178" t="n">
-        <v>0.94745</v>
+        <v>1.94745</v>
       </c>
       <c r="AZ23" s="178" t="n">
-        <v>0.9460500000000001</v>
+        <v>1.94605</v>
       </c>
       <c r="BA23" s="178" t="n">
-        <v>0.94245</v>
+        <v>1.94245</v>
       </c>
       <c r="BB23" s="178" t="n">
-        <v>0.94045</v>
+        <v>1.94045</v>
       </c>
     </row>
     <row r="24" ht="15" customHeight="1" thickBot="1">
@@ -3843,7 +3843,7 @@
         <v>498.9628260819919</v>
       </c>
       <c r="D24" s="80" t="n">
-        <v>531.9763172223447</v>
+        <v>531.9763172223448</v>
       </c>
       <c r="E24" s="80" t="n">
         <v>556.6558094887075</v>
@@ -3873,7 +3873,7 @@
         <v>500.8358548119919</v>
       </c>
       <c r="N24" s="80" t="n">
-        <v>534.3942127823448</v>
+        <v>534.3942127823449</v>
       </c>
       <c r="O24" s="80" t="n">
         <v>598.3903586987075</v>
@@ -3893,7 +3893,7 @@
         <v>610.469045192144</v>
       </c>
       <c r="U24" s="80" t="n">
-        <v>650.8602594498545</v>
+        <v>650.8602594498547</v>
       </c>
       <c r="V24" s="80" t="n">
         <v>681.0550260579738</v>
@@ -3923,7 +3923,7 @@
         <v>612.342073922144</v>
       </c>
       <c r="AE24" s="80" t="n">
-        <v>653.2781550098546</v>
+        <v>653.2781550098547</v>
       </c>
       <c r="AF24" s="80" t="n">
         <v>722.7895752679738</v>
@@ -4408,49 +4408,49 @@
         </is>
       </c>
       <c r="C35" s="148" t="n">
-        <v>252.4498024009512</v>
+        <v>257.3291969857196</v>
       </c>
       <c r="D35" s="149" t="n">
-        <v>284.3056120885324</v>
+        <v>290.5284948056334</v>
       </c>
       <c r="E35" s="149" t="n">
-        <v>313.9988433736508</v>
+        <v>322.8769702484412</v>
       </c>
       <c r="F35" s="149" t="n">
-        <v>346.9583558469386</v>
+        <v>359.1502061329732</v>
       </c>
       <c r="G35" s="150" t="n">
-        <v>374.7258202030197</v>
+        <v>389.5778259982649</v>
       </c>
       <c r="H35" s="148" t="n">
-        <v>38.09033249868336</v>
+        <v>38.82654920536517</v>
       </c>
       <c r="I35" s="149" t="n">
-        <v>44.43666812671998</v>
+        <v>45.4092981499543</v>
       </c>
       <c r="J35" s="149" t="n">
-        <v>49.66287220994334</v>
+        <v>51.06705980410496</v>
       </c>
       <c r="K35" s="149" t="n">
-        <v>57.32562416776201</v>
+        <v>59.34000259568827</v>
       </c>
       <c r="L35" s="150" t="n">
-        <v>62.89218967426555</v>
+        <v>65.3848793026765</v>
       </c>
       <c r="M35" s="151" t="n">
-        <v>9793665.078057555</v>
+        <v>9982958.774833802</v>
       </c>
       <c r="N35" s="152" t="n">
-        <v>11747875.19038999</v>
+        <v>12005012.74370066</v>
       </c>
       <c r="O35" s="152" t="n">
-        <v>13377579.88428444</v>
+        <v>13755822.84280703</v>
       </c>
       <c r="P35" s="152" t="n">
-        <v>15634429.6554371</v>
+        <v>16183811.51194646</v>
       </c>
       <c r="Q35" s="153" t="n">
-        <v>17416938.97993196</v>
+        <v>18107247.63954137</v>
       </c>
       <c r="S35" s="21" t="inlineStr">
         <is>
@@ -4458,49 +4458,49 @@
         </is>
       </c>
       <c r="T35" s="148" t="n">
-        <v>352.6143950521421</v>
+        <v>359.429788660556</v>
       </c>
       <c r="U35" s="149" t="n">
-        <v>397.1096450188747</v>
+        <v>405.801582995859</v>
       </c>
       <c r="V35" s="149" t="n">
-        <v>438.584269626091</v>
+        <v>450.9849738745273</v>
       </c>
       <c r="W35" s="149" t="n">
-        <v>484.6211389024763</v>
+        <v>501.6503537098956</v>
       </c>
       <c r="X35" s="150" t="n">
-        <v>523.4059093912274</v>
+        <v>544.150750500208</v>
       </c>
       <c r="Y35" s="148" t="n">
-        <v>48.15795795450825</v>
+        <v>49.08876351276938</v>
       </c>
       <c r="Z35" s="149" t="n">
-        <v>56.21569360302731</v>
+        <v>57.4461429971926</v>
       </c>
       <c r="AA35" s="149" t="n">
-        <v>62.84031849710248</v>
+        <v>64.61709039369708</v>
       </c>
       <c r="AB35" s="149" t="n">
-        <v>72.59358222781339</v>
+        <v>75.14446498170469</v>
       </c>
       <c r="AC35" s="150" t="n">
-        <v>79.66600871621333</v>
+        <v>82.82351737813637</v>
       </c>
       <c r="AD35" s="151" t="n">
-        <v>9793665.078057555</v>
+        <v>9982958.774833802</v>
       </c>
       <c r="AE35" s="152" t="n">
-        <v>11747875.19038999</v>
+        <v>12005012.74370066</v>
       </c>
       <c r="AF35" s="152" t="n">
-        <v>13377579.88428444</v>
+        <v>13755822.84280703</v>
       </c>
       <c r="AG35" s="152" t="n">
-        <v>15634429.6554371</v>
+        <v>16183811.51194646</v>
       </c>
       <c r="AH35" s="153" t="n">
-        <v>17416938.97993196</v>
+        <v>18107247.63954137</v>
       </c>
     </row>
     <row r="36" ht="15" customHeight="1" thickBot="1">
@@ -4510,49 +4510,49 @@
         </is>
       </c>
       <c r="C36" s="155" t="n">
-        <v>668.4758219127017</v>
+        <v>683.467967918176</v>
       </c>
       <c r="D36" s="156" t="n">
-        <v>737.2648517143355</v>
+        <v>756.1704238953171</v>
       </c>
       <c r="E36" s="156" t="n">
-        <v>797.8313589184903</v>
+        <v>823.9026125581048</v>
       </c>
       <c r="F36" s="156" t="n">
-        <v>856.9130089426513</v>
+        <v>891.1118444972583</v>
       </c>
       <c r="G36" s="157" t="n">
-        <v>905.3998678105238</v>
+        <v>946.3544124866283</v>
       </c>
       <c r="H36" s="155" t="n">
-        <v>21.32669275897923</v>
+        <v>21.8049941143546</v>
       </c>
       <c r="I36" s="156" t="n">
-        <v>25.39050150755473</v>
+        <v>26.04158633527467</v>
       </c>
       <c r="J36" s="156" t="n">
-        <v>29.30580767487365</v>
+        <v>30.26345259126437</v>
       </c>
       <c r="K36" s="156" t="n">
-        <v>34.59988440567489</v>
+        <v>35.9807430746991</v>
       </c>
       <c r="L36" s="157" t="n">
-        <v>39.11742307147171</v>
+        <v>40.88684706605301</v>
       </c>
       <c r="M36" s="158" t="n">
-        <v>5021984.393170478</v>
+        <v>5134614.230767592</v>
       </c>
       <c r="N36" s="159" t="n">
-        <v>6146410.52930356</v>
+        <v>6304022.014030513</v>
       </c>
       <c r="O36" s="159" t="n">
-        <v>7220293.369940395</v>
+        <v>7456235.587172013</v>
       </c>
       <c r="P36" s="159" t="n">
-        <v>8590435.582203966</v>
+        <v>8933274.225978013</v>
       </c>
       <c r="Q36" s="160" t="n">
-        <v>9792733.345782666</v>
+        <v>10235694.46116353</v>
       </c>
       <c r="S36" s="32" t="inlineStr">
         <is>
@@ -4560,49 +4560,49 @@
         </is>
       </c>
       <c r="T36" s="155" t="n">
-        <v>785.0108893938392</v>
+        <v>802.6166089784386</v>
       </c>
       <c r="U36" s="156" t="n">
-        <v>865.7918775687143</v>
+        <v>887.9932490256911</v>
       </c>
       <c r="V36" s="156" t="n">
-        <v>936.9169147492229</v>
+        <v>967.533157455932</v>
       </c>
       <c r="W36" s="156" t="n">
-        <v>1006.298240314023</v>
+        <v>1046.458942369244</v>
       </c>
       <c r="X36" s="157" t="n">
-        <v>1063.237789892456</v>
+        <v>1111.331920580562</v>
       </c>
       <c r="Y36" s="155" t="n">
-        <v>22.1360807018837</v>
+        <v>22.63253448972906</v>
       </c>
       <c r="Z36" s="156" t="n">
-        <v>26.36213626325571</v>
+        <v>27.03813657550572</v>
       </c>
       <c r="AA36" s="156" t="n">
-        <v>30.43564657044793</v>
+        <v>31.43021196644771</v>
       </c>
       <c r="AB36" s="156" t="n">
-        <v>35.9495584355905</v>
+        <v>37.38428170897911</v>
       </c>
       <c r="AC36" s="157" t="n">
-        <v>40.65712045864194</v>
+        <v>42.49619059265004</v>
       </c>
       <c r="AD36" s="158" t="n">
-        <v>5021984.393170478</v>
+        <v>5134614.230767592</v>
       </c>
       <c r="AE36" s="159" t="n">
-        <v>6146410.52930356</v>
+        <v>6304022.014030513</v>
       </c>
       <c r="AF36" s="159" t="n">
-        <v>7220293.369940395</v>
+        <v>7456235.587172013</v>
       </c>
       <c r="AG36" s="159" t="n">
-        <v>8590435.582203966</v>
+        <v>8933274.225978013</v>
       </c>
       <c r="AH36" s="160" t="n">
-        <v>9792733.345782666</v>
+        <v>10235694.46116353</v>
       </c>
     </row>
     <row r="37" ht="15" customHeight="1" thickTop="1">
@@ -4612,49 +4612,49 @@
         </is>
       </c>
       <c r="C37" s="161" t="n">
-        <v>319.9434062749648</v>
+        <v>326.4634339126046</v>
       </c>
       <c r="D37" s="162" t="n">
-        <v>360.3500327575788</v>
+        <v>368.7021308398481</v>
       </c>
       <c r="E37" s="162" t="n">
-        <v>398.7677147520914</v>
+        <v>410.6581277062482</v>
       </c>
       <c r="F37" s="162" t="n">
-        <v>439.7623541534582</v>
+        <v>455.9591413710377</v>
       </c>
       <c r="G37" s="163" t="n">
-        <v>474.9042135915144</v>
+        <v>494.6837458415284</v>
       </c>
       <c r="H37" s="161" t="n">
-        <v>30.07669660528159</v>
+        <v>30.6896202951257</v>
       </c>
       <c r="I37" s="162" t="n">
-        <v>35.33287344021524</v>
+        <v>36.1518094681734</v>
       </c>
       <c r="J37" s="162" t="n">
-        <v>39.93806608419666</v>
+        <v>41.12893505568983</v>
       </c>
       <c r="K37" s="162" t="n">
-        <v>46.49601204294458</v>
+        <v>48.20849608441119</v>
       </c>
       <c r="L37" s="163" t="n">
-        <v>51.60430474726942</v>
+        <v>53.75359923819201</v>
       </c>
       <c r="M37" s="164" t="n">
-        <v>14815649.47122803</v>
+        <v>15117573.00560139</v>
       </c>
       <c r="N37" s="165" t="n">
-        <v>17894285.71969355</v>
+        <v>18309034.75773117</v>
       </c>
       <c r="O37" s="165" t="n">
-        <v>20597873.25422484</v>
+        <v>21212058.42997904</v>
       </c>
       <c r="P37" s="165" t="n">
-        <v>24224865.23764107</v>
+        <v>25117085.73792448</v>
       </c>
       <c r="Q37" s="166" t="n">
-        <v>27209672.32571463</v>
+        <v>28342942.10070489</v>
       </c>
       <c r="S37" s="42" t="inlineStr">
         <is>
@@ -4662,49 +4662,49 @@
         </is>
       </c>
       <c r="T37" s="161" t="n">
-        <v>433.5639147910651</v>
+        <v>442.3993796003995</v>
       </c>
       <c r="U37" s="162" t="n">
-        <v>487.8135639500144</v>
+        <v>499.1199781628661</v>
       </c>
       <c r="V37" s="162" t="n">
-        <v>539.0960229634838</v>
+        <v>555.1707303629144</v>
       </c>
       <c r="W37" s="162" t="n">
-        <v>593.778597602929</v>
+        <v>615.6479220434911</v>
       </c>
       <c r="X37" s="163" t="n">
-        <v>640.4316929155569</v>
+        <v>667.1053651244334</v>
       </c>
       <c r="Y37" s="161" t="n">
-        <v>34.43624459755173</v>
+        <v>35.13801016642737</v>
       </c>
       <c r="Z37" s="162" t="n">
-        <v>40.47276409770219</v>
+        <v>41.41083115660533</v>
       </c>
       <c r="AA37" s="162" t="n">
-        <v>45.76150035782855</v>
+        <v>47.1260118679809</v>
       </c>
       <c r="AB37" s="162" t="n">
-        <v>53.32028973054803</v>
+        <v>55.28411719096772</v>
       </c>
       <c r="AC37" s="163" t="n">
-        <v>59.21763993817229</v>
+        <v>61.68402618071315</v>
       </c>
       <c r="AD37" s="164" t="n">
-        <v>14815649.47122803</v>
+        <v>15117573.00560139</v>
       </c>
       <c r="AE37" s="165" t="n">
-        <v>17894285.71969355</v>
+        <v>18309034.75773117</v>
       </c>
       <c r="AF37" s="165" t="n">
-        <v>20597873.25422484</v>
+        <v>21212058.42997904</v>
       </c>
       <c r="AG37" s="165" t="n">
-        <v>24224865.23764107</v>
+        <v>25117085.73792448</v>
       </c>
       <c r="AH37" s="166" t="n">
-        <v>27209672.32571463</v>
+        <v>28342942.10070489</v>
       </c>
     </row>
     <row r="38" ht="15" customHeight="1" thickBot="1">
@@ -4714,49 +4714,49 @@
         </is>
       </c>
       <c r="C38" s="155" t="n">
-        <v>875.9758032286693</v>
+        <v>889.8881545315182</v>
       </c>
       <c r="D38" s="156" t="n">
-        <v>987.2527041438691</v>
+        <v>1004.965408435306</v>
       </c>
       <c r="E38" s="156" t="n">
-        <v>1054.131057515784</v>
+        <v>1079.48029491429</v>
       </c>
       <c r="F38" s="156" t="n">
-        <v>1124.579794293967</v>
+        <v>1160.17744141469</v>
       </c>
       <c r="G38" s="157" t="n">
-        <v>1185.223372230543</v>
+        <v>1230.567171681688</v>
       </c>
       <c r="H38" s="155" t="n">
-        <v>39.33296175371753</v>
+        <v>39.9576525039441</v>
       </c>
       <c r="I38" s="156" t="n">
-        <v>47.12034178884424</v>
+        <v>47.96574710068989</v>
       </c>
       <c r="J38" s="156" t="n">
-        <v>53.69064307268995</v>
+        <v>54.98176987103656</v>
       </c>
       <c r="K38" s="156" t="n">
-        <v>64.23359108358756</v>
+        <v>66.26685250291256</v>
       </c>
       <c r="L38" s="157" t="n">
-        <v>75.58684382404253</v>
+        <v>78.47861491783411</v>
       </c>
       <c r="M38" s="158" t="n">
-        <v>146823.6151242986</v>
+        <v>149155.4851435784</v>
       </c>
       <c r="N38" s="159" t="n">
-        <v>180468.6838619842</v>
+        <v>183706.5462833225</v>
       </c>
       <c r="O38" s="159" t="n">
-        <v>209082.672788576</v>
+        <v>214110.5924866468</v>
       </c>
       <c r="P38" s="159" t="n">
-        <v>252730.3282761496</v>
+        <v>260730.2986547096</v>
       </c>
       <c r="Q38" s="160" t="n">
-        <v>300958.5098573974</v>
+        <v>312472.4595767715</v>
       </c>
       <c r="S38" s="32" t="inlineStr">
         <is>
@@ -4764,49 +4764,49 @@
         </is>
       </c>
       <c r="T38" s="155" t="n">
-        <v>950.6988929505061</v>
+        <v>965.798005201332</v>
       </c>
       <c r="U38" s="156" t="n">
-        <v>1071.468012509654</v>
+        <v>1090.691658070366</v>
       </c>
       <c r="V38" s="156" t="n">
-        <v>1144.051269123233</v>
+        <v>1171.562864584059</v>
       </c>
       <c r="W38" s="156" t="n">
-        <v>1220.509472441089</v>
+        <v>1259.14369451044</v>
       </c>
       <c r="X38" s="157" t="n">
-        <v>1286.326110522141</v>
+        <v>1335.537857903159</v>
       </c>
       <c r="Y38" s="155" t="n">
-        <v>40.03487534649717</v>
+        <v>40.67071397141503</v>
       </c>
       <c r="Z38" s="156" t="n">
-        <v>47.97004935029909</v>
+        <v>48.83069961281144</v>
       </c>
       <c r="AA38" s="156" t="n">
-        <v>54.6702351064912</v>
+        <v>55.98491866359324</v>
       </c>
       <c r="AB38" s="156" t="n">
-        <v>65.43188436213913</v>
+        <v>67.50307676821443</v>
       </c>
       <c r="AC38" s="157" t="n">
-        <v>77.03032983176023</v>
+        <v>79.9773252331195</v>
       </c>
       <c r="AD38" s="158" t="n">
-        <v>146823.6151242986</v>
+        <v>149155.4851435784</v>
       </c>
       <c r="AE38" s="159" t="n">
-        <v>180468.6838619842</v>
+        <v>183706.5462833225</v>
       </c>
       <c r="AF38" s="159" t="n">
-        <v>209082.672788576</v>
+        <v>214110.5924866468</v>
       </c>
       <c r="AG38" s="159" t="n">
-        <v>252730.3282761496</v>
+        <v>260730.2986547096</v>
       </c>
       <c r="AH38" s="160" t="n">
-        <v>300958.5098573974</v>
+        <v>312472.4595767715</v>
       </c>
     </row>
     <row r="39" ht="15" customHeight="1" thickTop="1">
@@ -4816,49 +4816,49 @@
         </is>
       </c>
       <c r="C39" s="161" t="n">
-        <v>321.948742738072</v>
+        <v>328.4954308657734</v>
       </c>
       <c r="D39" s="162" t="n">
-        <v>362.6492926804748</v>
+        <v>371.0357221951867</v>
       </c>
       <c r="E39" s="162" t="n">
-        <v>401.2746246785176</v>
+        <v>413.2165206168391</v>
       </c>
       <c r="F39" s="162" t="n">
-        <v>442.5448236225008</v>
+        <v>458.8204381262875</v>
       </c>
       <c r="G39" s="163" t="n">
-        <v>478.0383808327267</v>
+        <v>497.9307112352794</v>
       </c>
       <c r="H39" s="161" t="n">
-        <v>30.14631209115986</v>
+        <v>30.75932427994092</v>
       </c>
       <c r="I39" s="162" t="n">
-        <v>35.42134559586075</v>
+        <v>36.24048029197518</v>
       </c>
       <c r="J39" s="162" t="n">
-        <v>40.04112872980019</v>
+        <v>41.23274903952522</v>
       </c>
       <c r="K39" s="162" t="n">
-        <v>46.62895840631368</v>
+        <v>48.34384673225109</v>
       </c>
       <c r="L39" s="163" t="n">
-        <v>51.78404734710321</v>
+        <v>53.93890649798477</v>
       </c>
       <c r="M39" s="164" t="n">
-        <v>14962473.08635233</v>
+        <v>15266728.49074497</v>
       </c>
       <c r="N39" s="165" t="n">
-        <v>18074754.40355553</v>
+        <v>18492741.30401449</v>
       </c>
       <c r="O39" s="165" t="n">
-        <v>20806955.92701341</v>
+        <v>21426169.02246569</v>
       </c>
       <c r="P39" s="165" t="n">
-        <v>24477595.56591722</v>
+        <v>25377816.03657918</v>
       </c>
       <c r="Q39" s="166" t="n">
-        <v>27510630.83557203</v>
+        <v>28655414.56028166</v>
       </c>
       <c r="S39" s="42" t="inlineStr">
         <is>
@@ -4866,49 +4866,49 @@
         </is>
       </c>
       <c r="T39" s="161" t="n">
-        <v>435.8905640802653</v>
+        <v>444.7542097543313</v>
       </c>
       <c r="U39" s="162" t="n">
-        <v>490.4812112645882</v>
+        <v>501.8238119247395</v>
       </c>
       <c r="V39" s="162" t="n">
-        <v>541.9758552433904</v>
+        <v>558.1050068676293</v>
       </c>
       <c r="W39" s="162" t="n">
-        <v>596.9435106132358</v>
+        <v>618.8974957028133</v>
       </c>
       <c r="X39" s="163" t="n">
-        <v>643.9690714330973</v>
+        <v>670.7661782169868</v>
       </c>
       <c r="Y39" s="161" t="n">
-        <v>34.48356495677098</v>
+        <v>35.18477330249506</v>
       </c>
       <c r="Z39" s="162" t="n">
-        <v>40.53602049109928</v>
+        <v>41.47343436592806</v>
       </c>
       <c r="AA39" s="162" t="n">
-        <v>45.83655655678243</v>
+        <v>47.20064826582237</v>
       </c>
       <c r="AB39" s="162" t="n">
-        <v>53.42238927713217</v>
+        <v>55.3871218134402</v>
       </c>
       <c r="AC39" s="163" t="n">
-        <v>59.36782438609148</v>
+        <v>61.83826279714889</v>
       </c>
       <c r="AD39" s="164" t="n">
-        <v>14962473.08635233</v>
+        <v>15266728.49074497</v>
       </c>
       <c r="AE39" s="165" t="n">
-        <v>18074754.40355553</v>
+        <v>18492741.30401449</v>
       </c>
       <c r="AF39" s="165" t="n">
-        <v>20806955.92701341</v>
+        <v>21426169.02246569</v>
       </c>
       <c r="AG39" s="165" t="n">
-        <v>24477595.56591722</v>
+        <v>25377816.03657918</v>
       </c>
       <c r="AH39" s="166" t="n">
-        <v>27510630.83557203</v>
+        <v>28655414.56028166</v>
       </c>
     </row>
     <row r="40" ht="15" customHeight="1" thickBot="1">
@@ -4918,34 +4918,34 @@
         </is>
       </c>
       <c r="C40" s="155" t="n">
-        <v>3903.157151386098</v>
+        <v>3903.157151386096</v>
       </c>
       <c r="D40" s="156" t="n">
-        <v>4343.945887805072</v>
+        <v>4343.945887805071</v>
       </c>
       <c r="E40" s="156" t="n">
-        <v>4467.656743127437</v>
+        <v>4507.461976017251</v>
       </c>
       <c r="F40" s="156" t="n">
-        <v>4939.927426339694</v>
+        <v>5025.691357533317</v>
       </c>
       <c r="G40" s="157" t="n">
-        <v>5387.514444619565</v>
+        <v>5524.228547515234</v>
       </c>
       <c r="H40" s="155" t="n">
-        <v>3888.560102448786</v>
+        <v>3888.560102448784</v>
       </c>
       <c r="I40" s="156" t="n">
-        <v>4324.291469355592</v>
+        <v>4324.291469355591</v>
       </c>
       <c r="J40" s="156" t="n">
-        <v>4156.061414945819</v>
+        <v>4193.090444264325</v>
       </c>
       <c r="K40" s="156" t="n">
-        <v>4530.277702660615</v>
+        <v>4608.929551492913</v>
       </c>
       <c r="L40" s="157" t="n">
-        <v>4952.596524800791</v>
+        <v>5078.274107265289</v>
       </c>
       <c r="M40" s="158" t="n">
         <v>1947530.322897744</v>
@@ -4954,13 +4954,13 @@
         <v>2310876.335607691</v>
       </c>
       <c r="O40" s="159" t="n">
-        <v>2486947.080863286</v>
+        <v>2509104.894999452</v>
       </c>
       <c r="P40" s="159" t="n">
-        <v>2908910.328771539</v>
+        <v>2959413.011048805</v>
       </c>
       <c r="Q40" s="160" t="n">
-        <v>3429598.299762174</v>
+        <v>3516628.127647416</v>
       </c>
       <c r="S40" s="32" t="inlineStr">
         <is>
@@ -4968,34 +4968,34 @@
         </is>
       </c>
       <c r="T40" s="155" t="n">
-        <v>3190.219615942628</v>
+        <v>3190.219615942627</v>
       </c>
       <c r="U40" s="156" t="n">
         <v>3550.495366794985</v>
       </c>
       <c r="V40" s="156" t="n">
-        <v>3651.609614068965</v>
+        <v>3684.144157223895</v>
       </c>
       <c r="W40" s="156" t="n">
-        <v>4037.616925376766</v>
+        <v>4107.715505839275</v>
       </c>
       <c r="X40" s="157" t="n">
-        <v>4403.449206828882</v>
+        <v>4515.191572282672</v>
       </c>
       <c r="Y40" s="155" t="n">
-        <v>3180.461388882715</v>
+        <v>3180.461388882714</v>
       </c>
       <c r="Z40" s="156" t="n">
         <v>3537.354368711183</v>
       </c>
       <c r="AA40" s="156" t="n">
-        <v>3440.762243895469</v>
+        <v>3471.418211959135</v>
       </c>
       <c r="AB40" s="156" t="n">
-        <v>3759.741362533297</v>
+        <v>3825.015641220637</v>
       </c>
       <c r="AC40" s="157" t="n">
-        <v>4108.553884095334</v>
+        <v>4212.812956481408</v>
       </c>
       <c r="AD40" s="158" t="n">
         <v>1947530.322897744</v>
@@ -5004,13 +5004,13 @@
         <v>2310876.335607691</v>
       </c>
       <c r="AF40" s="159" t="n">
-        <v>2486947.080863286</v>
+        <v>2509104.894999452</v>
       </c>
       <c r="AG40" s="159" t="n">
-        <v>2908910.328771539</v>
+        <v>2959413.011048805</v>
       </c>
       <c r="AH40" s="160" t="n">
-        <v>3429598.299762174</v>
+        <v>3516628.127647416</v>
       </c>
     </row>
     <row r="41" ht="15.6" customHeight="1" thickBot="1" thickTop="1">
@@ -5020,49 +5020,49 @@
         </is>
       </c>
       <c r="C41" s="179" t="n">
-        <v>359.9889878884621</v>
+        <v>366.4661359076628</v>
       </c>
       <c r="D41" s="180" t="n">
-        <v>404.6948761566285</v>
+        <v>412.9927384636977</v>
       </c>
       <c r="E41" s="180" t="n">
-        <v>444.4653590489198</v>
+        <v>456.7032030683341</v>
       </c>
       <c r="F41" s="180" t="n">
-        <v>489.9208819966501</v>
+        <v>506.9284961630472</v>
       </c>
       <c r="G41" s="181" t="n">
-        <v>531.7507818103561</v>
+        <v>552.921207432346</v>
       </c>
       <c r="H41" s="179" t="n">
-        <v>34.03584100856929</v>
+        <v>34.64823524169174</v>
       </c>
       <c r="I41" s="180" t="n">
-        <v>39.90820757769603</v>
+        <v>40.72648532449282</v>
       </c>
       <c r="J41" s="180" t="n">
-        <v>44.77547517037822</v>
+        <v>46.00831653781972</v>
       </c>
       <c r="K41" s="180" t="n">
-        <v>52.10659419254768</v>
+        <v>53.91547575305634</v>
       </c>
       <c r="L41" s="181" t="n">
-        <v>58.16386265635766</v>
+        <v>60.47952211634357</v>
       </c>
       <c r="M41" s="182" t="n">
-        <v>16910003.40925008</v>
+        <v>17214258.81364272</v>
       </c>
       <c r="N41" s="183" t="n">
-        <v>20385630.73916322</v>
+        <v>20803617.63962218</v>
       </c>
       <c r="O41" s="183" t="n">
-        <v>23293903.0078767</v>
+        <v>23935273.91746514</v>
       </c>
       <c r="P41" s="183" t="n">
-        <v>27386505.89468876</v>
+        <v>28337229.04762799</v>
       </c>
       <c r="Q41" s="184" t="n">
-        <v>30940229.1353342</v>
+        <v>32172042.68792908</v>
       </c>
       <c r="S41" s="51" t="inlineStr">
         <is>
@@ -5070,49 +5070,49 @@
         </is>
       </c>
       <c r="T41" s="185" t="n">
-        <v>484.0185615432303</v>
+        <v>492.727327568394</v>
       </c>
       <c r="U41" s="186" t="n">
-        <v>543.5889292745327</v>
+        <v>554.7346747546941</v>
       </c>
       <c r="V41" s="186" t="n">
-        <v>596.1791883625166</v>
+        <v>612.5942987108541</v>
       </c>
       <c r="W41" s="186" t="n">
-        <v>656.3520526965516</v>
+        <v>679.1373286049625</v>
       </c>
       <c r="X41" s="187" t="n">
-        <v>711.2816345803684</v>
+        <v>739.5996652373341</v>
       </c>
       <c r="Y41" s="185" t="n">
-        <v>38.91705837834751</v>
+        <v>39.6172785408224</v>
       </c>
       <c r="Z41" s="186" t="n">
-        <v>45.65170903531456</v>
+        <v>46.58775151565181</v>
       </c>
       <c r="AA41" s="186" t="n">
-        <v>51.23358401195283</v>
+        <v>52.6442420012177</v>
       </c>
       <c r="AB41" s="186" t="n">
-        <v>59.67033110976517</v>
+        <v>61.74178796328828</v>
       </c>
       <c r="AC41" s="187" t="n">
-        <v>66.64882321318056</v>
+        <v>69.30229172304165</v>
       </c>
       <c r="AD41" s="188" t="n">
-        <v>16910003.40925008</v>
+        <v>17214258.81364272</v>
       </c>
       <c r="AE41" s="189" t="n">
-        <v>20385630.73916322</v>
+        <v>20803617.63962218</v>
       </c>
       <c r="AF41" s="189" t="n">
-        <v>23293903.0078767</v>
+        <v>23935273.91746514</v>
       </c>
       <c r="AG41" s="189" t="n">
-        <v>27386505.89468876</v>
+        <v>28337229.04762799</v>
       </c>
       <c r="AH41" s="190" t="n">
-        <v>30940229.1353342</v>
+        <v>32172042.68792908</v>
       </c>
     </row>
     <row r="42" ht="15" customHeight="1" thickBot="1"/>
@@ -6334,49 +6334,49 @@
         </is>
       </c>
       <c r="C57" s="148" t="n">
-        <v>0.1601028446281168</v>
+        <v>0.1568385499250627</v>
       </c>
       <c r="D57" s="149" t="n">
-        <v>0.0763552678881472</v>
+        <v>0.0744327113924572</v>
       </c>
       <c r="E57" s="149" t="n">
-        <v>0.05837663786780946</v>
+        <v>0.0563676138326108</v>
       </c>
       <c r="F57" s="149" t="n">
-        <v>0.03994201092333402</v>
+        <v>0.03811604984477479</v>
       </c>
       <c r="G57" s="150" t="n">
-        <v>0.0237311524098678</v>
+        <v>0.02246747382007142</v>
       </c>
       <c r="H57" s="148" t="n">
-        <v>0.02415676513853762</v>
+        <v>0.02366423922078887</v>
       </c>
       <c r="I57" s="149" t="n">
-        <v>0.01193424805774087</v>
+        <v>0.01163375449967757</v>
       </c>
       <c r="J57" s="149" t="n">
-        <v>0.009233000591104861</v>
+        <v>0.008915248134265244</v>
       </c>
       <c r="K57" s="149" t="n">
-        <v>0.006599353115754897</v>
+        <v>0.006297661697259056</v>
       </c>
       <c r="L57" s="150" t="n">
-        <v>0.003982923134951571</v>
+        <v>0.003770833363518889</v>
       </c>
       <c r="M57" s="151" t="n">
-        <v>6211.110578893263</v>
+        <v>6084.473882275796</v>
       </c>
       <c r="N57" s="152" t="n">
-        <v>3155.098313709746</v>
+        <v>3075.655795526861</v>
       </c>
       <c r="O57" s="152" t="n">
-        <v>2487.073290022499</v>
+        <v>2401.48100174666</v>
       </c>
       <c r="P57" s="152" t="n">
-        <v>1799.842976985551</v>
+        <v>1717.562612338866</v>
       </c>
       <c r="Q57" s="153" t="n">
-        <v>1103.003879535713</v>
+        <v>1044.269168175802</v>
       </c>
       <c r="S57" s="21" t="inlineStr">
         <is>
@@ -6384,49 +6384,49 @@
         </is>
       </c>
       <c r="T57" s="148" t="n">
-        <v>0.223626903914177</v>
+        <v>0.2190674339084878</v>
       </c>
       <c r="U57" s="149" t="n">
-        <v>0.1066507731016621</v>
+        <v>0.1039654032212587</v>
       </c>
       <c r="V57" s="149" t="n">
-        <v>0.08153875602660419</v>
+        <v>0.0787326108520809</v>
       </c>
       <c r="W57" s="149" t="n">
-        <v>0.05578981597509227</v>
+        <v>0.05323936770782718</v>
       </c>
       <c r="X57" s="150" t="n">
-        <v>0.03314696969976392</v>
+        <v>0.03138190093265238</v>
       </c>
       <c r="Y57" s="148" t="n">
-        <v>0.03054162049908169</v>
+        <v>0.02991891544815388</v>
       </c>
       <c r="Z57" s="149" t="n">
-        <v>0.01509771232810036</v>
+        <v>0.01471756560464221</v>
       </c>
       <c r="AA57" s="149" t="n">
-        <v>0.01168286633475859</v>
+        <v>0.01128080208227984</v>
       </c>
       <c r="AB57" s="149" t="n">
-        <v>0.008357007708401764</v>
+        <v>0.007974964579976138</v>
       </c>
       <c r="AC57" s="150" t="n">
-        <v>0.005045198630043803</v>
+        <v>0.004776542924667886</v>
       </c>
       <c r="AD57" s="151" t="n">
-        <v>6211.110578893263</v>
+        <v>6084.473882275796</v>
       </c>
       <c r="AE57" s="152" t="n">
-        <v>3155.098313709746</v>
+        <v>3075.655795526861</v>
       </c>
       <c r="AF57" s="152" t="n">
-        <v>2487.073290022499</v>
+        <v>2401.48100174666</v>
       </c>
       <c r="AG57" s="152" t="n">
-        <v>1799.842976985551</v>
+        <v>1717.562612338866</v>
       </c>
       <c r="AH57" s="153" t="n">
-        <v>1103.003879535713</v>
+        <v>1044.269168175802</v>
       </c>
     </row>
     <row r="58" ht="15" customHeight="1" thickBot="1">
@@ -6436,49 +6436,49 @@
         </is>
       </c>
       <c r="C58" s="155" t="n">
-        <v>0.2773194171680923</v>
+        <v>0.2709109515978836</v>
       </c>
       <c r="D58" s="156" t="n">
-        <v>0.05609682008471065</v>
+        <v>0.05449122229132964</v>
       </c>
       <c r="E58" s="156" t="n">
-        <v>0.04119876279439155</v>
+        <v>0.03962298779200776</v>
       </c>
       <c r="F58" s="156" t="n">
-        <v>0.02689540012736986</v>
+        <v>0.0255650666188414</v>
       </c>
       <c r="G58" s="157" t="n">
-        <v>0.01496350996974041</v>
+        <v>0.01410600214889206</v>
       </c>
       <c r="H58" s="155" t="n">
-        <v>0.008847449394834603</v>
+        <v>0.008642997159178146</v>
       </c>
       <c r="I58" s="156" t="n">
-        <v>0.001931906005851137</v>
+        <v>0.001876611177814003</v>
       </c>
       <c r="J58" s="156" t="n">
-        <v>0.001513306045693458</v>
+        <v>0.001455424942572453</v>
       </c>
       <c r="K58" s="156" t="n">
-        <v>0.001085965233039949</v>
+        <v>0.00103224987904751</v>
       </c>
       <c r="L58" s="157" t="n">
-        <v>0.0006464921974596704</v>
+        <v>0.0006094439302710117</v>
       </c>
       <c r="M58" s="158" t="n">
-        <v>2083.386921843179</v>
+        <v>2035.242751145018</v>
       </c>
       <c r="N58" s="159" t="n">
-        <v>467.6665174358654</v>
+        <v>454.281011318062</v>
       </c>
       <c r="O58" s="159" t="n">
-        <v>372.8446500991481</v>
+        <v>358.5840451792656</v>
       </c>
       <c r="P58" s="159" t="n">
-        <v>269.6227036357591</v>
+        <v>256.2862923681062</v>
       </c>
       <c r="Q58" s="160" t="n">
-        <v>161.8441400979903</v>
+        <v>152.5694033435021</v>
       </c>
       <c r="S58" s="32" t="inlineStr">
         <is>
@@ -6486,49 +6486,49 @@
         </is>
       </c>
       <c r="T58" s="155" t="n">
-        <v>0.3256643773508613</v>
+        <v>0.3181387270700105</v>
       </c>
       <c r="U58" s="156" t="n">
-        <v>0.06587615166224482</v>
+        <v>0.06399065078027662</v>
       </c>
       <c r="V58" s="156" t="n">
-        <v>0.04838092323311387</v>
+        <v>0.04653044413490735</v>
       </c>
       <c r="W58" s="156" t="n">
-        <v>0.03158406225400778</v>
+        <v>0.03002181234684998</v>
       </c>
       <c r="X58" s="157" t="n">
-        <v>0.01757209144257355</v>
+        <v>0.01656509469708131</v>
       </c>
       <c r="Y58" s="155" t="n">
-        <v>0.0091832266738795</v>
+        <v>0.008971015092866014</v>
       </c>
       <c r="Z58" s="156" t="n">
-        <v>0.002005835503441954</v>
+        <v>0.001948424672429637</v>
       </c>
       <c r="AA58" s="156" t="n">
-        <v>0.001571649158099745</v>
+        <v>0.001511536540926973</v>
       </c>
       <c r="AB58" s="156" t="n">
-        <v>0.00112832661943189</v>
+        <v>0.001072515934211135</v>
       </c>
       <c r="AC58" s="157" t="n">
-        <v>0.0006719387189607388</v>
+        <v>0.0006334321982443531</v>
       </c>
       <c r="AD58" s="158" t="n">
-        <v>2083.386921843179</v>
+        <v>2035.242751145018</v>
       </c>
       <c r="AE58" s="159" t="n">
-        <v>467.6665174358654</v>
+        <v>454.281011318062</v>
       </c>
       <c r="AF58" s="159" t="n">
-        <v>372.8446500991481</v>
+        <v>358.5840451792656</v>
       </c>
       <c r="AG58" s="159" t="n">
-        <v>269.6227036357591</v>
+        <v>256.2862923681062</v>
       </c>
       <c r="AH58" s="160" t="n">
-        <v>161.8441400979903</v>
+        <v>152.5694033435021</v>
       </c>
     </row>
     <row r="59" ht="15" customHeight="1" thickTop="1">
@@ -6538,49 +6538,49 @@
         </is>
       </c>
       <c r="C59" s="161" t="n">
-        <v>0.1791193689401478</v>
+        <v>0.1753449825287217</v>
       </c>
       <c r="D59" s="162" t="n">
-        <v>0.07295420705949712</v>
+        <v>0.07108486272681104</v>
       </c>
       <c r="E59" s="162" t="n">
-        <v>0.05536702392937102</v>
+        <v>0.05343390639147785</v>
       </c>
       <c r="F59" s="162" t="n">
-        <v>0.03756772599649911</v>
+        <v>0.03583196160482287</v>
       </c>
       <c r="G59" s="163" t="n">
-        <v>0.02207603409869994</v>
+        <v>0.02088903070200566</v>
       </c>
       <c r="H59" s="161" t="n">
-        <v>0.01683834956458634</v>
+        <v>0.01648353345417087</v>
       </c>
       <c r="I59" s="162" t="n">
-        <v>0.007153271904094909</v>
+        <v>0.006969979824953031</v>
       </c>
       <c r="J59" s="162" t="n">
-        <v>0.005545212861455507</v>
+        <v>0.005351603968055262</v>
       </c>
       <c r="K59" s="162" t="n">
-        <v>0.003972030402015094</v>
+        <v>0.003788508276265035</v>
       </c>
       <c r="L59" s="163" t="n">
-        <v>0.002398838247032935</v>
+        <v>0.002269855426358821</v>
       </c>
       <c r="M59" s="164" t="n">
-        <v>8294.497500736441</v>
+        <v>8119.716633420814</v>
       </c>
       <c r="N59" s="165" t="n">
-        <v>3622.764831145612</v>
+        <v>3529.936806844923</v>
       </c>
       <c r="O59" s="165" t="n">
-        <v>2859.917940121647</v>
+        <v>2760.065046925926</v>
       </c>
       <c r="P59" s="165" t="n">
-        <v>2069.46568062131</v>
+        <v>1973.848904706972</v>
       </c>
       <c r="Q59" s="166" t="n">
-        <v>1264.848019633703</v>
+        <v>1196.838571519304</v>
       </c>
       <c r="S59" s="42" t="inlineStr">
         <is>
@@ -6588,49 +6588,49 @@
         </is>
       </c>
       <c r="T59" s="161" t="n">
-        <v>0.2427294743053824</v>
+        <v>0.2376147017663112</v>
       </c>
       <c r="U59" s="162" t="n">
-        <v>0.09875967397172968</v>
+        <v>0.09622910247656676</v>
       </c>
       <c r="V59" s="162" t="n">
-        <v>0.07485095031377892</v>
+        <v>0.07223755926418743</v>
       </c>
       <c r="W59" s="162" t="n">
-        <v>0.05072492323785447</v>
+        <v>0.04838124889528225</v>
       </c>
       <c r="X59" s="163" t="n">
-        <v>0.02977061791844373</v>
+        <v>0.02816988544843177</v>
       </c>
       <c r="Y59" s="161" t="n">
-        <v>0.01927902960338237</v>
+        <v>0.01887278371388953</v>
       </c>
       <c r="Z59" s="162" t="n">
-        <v>0.008193861922694239</v>
+        <v>0.007983906253715355</v>
       </c>
       <c r="AA59" s="162" t="n">
-        <v>0.0063537693539984</v>
+        <v>0.006131930033438011</v>
       </c>
       <c r="AB59" s="162" t="n">
-        <v>0.004555010258909451</v>
+        <v>0.004344552361833866</v>
       </c>
       <c r="AC59" s="163" t="n">
-        <v>0.002752745924558345</v>
+        <v>0.002604733888153694</v>
       </c>
       <c r="AD59" s="164" t="n">
-        <v>8294.497500736441</v>
+        <v>8119.716633420814</v>
       </c>
       <c r="AE59" s="165" t="n">
-        <v>3622.764831145612</v>
+        <v>3529.936806844923</v>
       </c>
       <c r="AF59" s="165" t="n">
-        <v>2859.917940121647</v>
+        <v>2760.065046925926</v>
       </c>
       <c r="AG59" s="165" t="n">
-        <v>2069.46568062131</v>
+        <v>1973.848904706972</v>
       </c>
       <c r="AH59" s="166" t="n">
-        <v>1264.848019633703</v>
+        <v>1196.838571519304</v>
       </c>
     </row>
     <row r="60" ht="15" customHeight="1" thickBot="1">
@@ -6640,7 +6640,7 @@
         </is>
       </c>
       <c r="C60" s="155" t="n">
-        <v>0.1889297589627878</v>
+        <v>0.1855701493505047</v>
       </c>
       <c r="D60" s="156" t="n">
         <v>0</v>
@@ -6655,7 +6655,7 @@
         <v>0</v>
       </c>
       <c r="H60" s="155" t="n">
-        <v>0.008483301657457466</v>
+        <v>0.008332448864605995</v>
       </c>
       <c r="I60" s="156" t="n">
         <v>0</v>
@@ -6670,7 +6670,7 @@
         <v>0</v>
       </c>
       <c r="M60" s="158" t="n">
-        <v>31.66679960021411</v>
+        <v>31.103690406029</v>
       </c>
       <c r="N60" s="159" t="n">
         <v>0</v>
@@ -6690,7 +6690,7 @@
         </is>
       </c>
       <c r="T60" s="155" t="n">
-        <v>0.2050459750478298</v>
+        <v>0.2013997817085034</v>
       </c>
       <c r="U60" s="156" t="n">
         <v>0</v>
@@ -6705,7 +6705,7 @@
         <v>0</v>
       </c>
       <c r="Y60" s="155" t="n">
-        <v>0.008634689818417826</v>
+        <v>0.008481144992699008</v>
       </c>
       <c r="Z60" s="156" t="n">
         <v>0</v>
@@ -6720,7 +6720,7 @@
         <v>0</v>
       </c>
       <c r="AD60" s="158" t="n">
-        <v>31.66679960021411</v>
+        <v>31.103690406029</v>
       </c>
       <c r="AE60" s="159" t="n">
         <v>0</v>
@@ -6742,49 +6742,49 @@
         </is>
       </c>
       <c r="C61" s="161" t="n">
-        <v>0.1791547502109828</v>
+        <v>0.1753818596962778</v>
       </c>
       <c r="D61" s="162" t="n">
-        <v>0.07268663652238706</v>
+        <v>0.07082414829145715</v>
       </c>
       <c r="E61" s="162" t="n">
-        <v>0.05515523280095683</v>
+        <v>0.0532295098657649</v>
       </c>
       <c r="F61" s="162" t="n">
-        <v>0.03741508524221988</v>
+        <v>0.03568637340373841</v>
       </c>
       <c r="G61" s="163" t="n">
-        <v>0.02197862720484592</v>
+        <v>0.02079686126671641</v>
       </c>
       <c r="H61" s="161" t="n">
-        <v>0.01677551204748158</v>
+        <v>0.01642222992569176</v>
       </c>
       <c r="I61" s="162" t="n">
-        <v>0.007099582225653702</v>
+        <v>0.006917665865612381</v>
       </c>
       <c r="J61" s="162" t="n">
-        <v>0.005503656700132831</v>
+        <v>0.005311498723515885</v>
       </c>
       <c r="K61" s="162" t="n">
-        <v>0.003942259315671832</v>
+        <v>0.003760112721450644</v>
       </c>
       <c r="L61" s="163" t="n">
-        <v>0.002380859607585204</v>
+        <v>0.002252843478029476</v>
       </c>
       <c r="M61" s="164" t="n">
-        <v>8326.164300336655</v>
+        <v>8150.820323826843</v>
       </c>
       <c r="N61" s="165" t="n">
-        <v>3622.764831145612</v>
+        <v>3529.936806844923</v>
       </c>
       <c r="O61" s="165" t="n">
-        <v>2859.917940121647</v>
+        <v>2760.065046925926</v>
       </c>
       <c r="P61" s="165" t="n">
-        <v>2069.46568062131</v>
+        <v>1973.848904706972</v>
       </c>
       <c r="Q61" s="166" t="n">
-        <v>1264.848019633703</v>
+        <v>1196.838571519304</v>
       </c>
       <c r="S61" s="42" t="inlineStr">
         <is>
@@ -6792,49 +6792,49 @@
         </is>
       </c>
       <c r="T61" s="161" t="n">
-        <v>0.2425599319412704</v>
+        <v>0.2374517667076331</v>
       </c>
       <c r="U61" s="162" t="n">
-        <v>0.09830828363330418</v>
+        <v>0.09578927835214007</v>
       </c>
       <c r="V61" s="162" t="n">
-        <v>0.07449462943836926</v>
+        <v>0.07189367918989886</v>
       </c>
       <c r="W61" s="162" t="n">
-        <v>0.05046876868101417</v>
+        <v>0.04813692960253461</v>
       </c>
       <c r="X61" s="163" t="n">
-        <v>0.02960757278071234</v>
+        <v>0.02801560706343488</v>
       </c>
       <c r="Y61" s="161" t="n">
-        <v>0.01918906225156673</v>
+        <v>0.01878495222451046</v>
       </c>
       <c r="Z61" s="162" t="n">
-        <v>0.008124728344904349</v>
+        <v>0.007916544122248424</v>
       </c>
       <c r="AA61" s="162" t="n">
-        <v>0.006300238769667966</v>
+        <v>0.006080268448089984</v>
       </c>
       <c r="AB61" s="162" t="n">
-        <v>0.004516611972286836</v>
+        <v>0.004307928214498445</v>
       </c>
       <c r="AC61" s="163" t="n">
-        <v>0.00272953664906928</v>
+        <v>0.002582772549169763</v>
       </c>
       <c r="AD61" s="164" t="n">
-        <v>8326.164300336655</v>
+        <v>8150.820323826843</v>
       </c>
       <c r="AE61" s="165" t="n">
-        <v>3622.764831145612</v>
+        <v>3529.936806844923</v>
       </c>
       <c r="AF61" s="165" t="n">
-        <v>2859.917940121647</v>
+        <v>2760.065046925926</v>
       </c>
       <c r="AG61" s="165" t="n">
-        <v>2069.46568062131</v>
+        <v>1973.848904706972</v>
       </c>
       <c r="AH61" s="166" t="n">
-        <v>1264.848019633703</v>
+        <v>1196.838571519304</v>
       </c>
     </row>
     <row r="62" ht="15" customHeight="1" thickBot="1">
@@ -6946,49 +6946,49 @@
         </is>
       </c>
       <c r="C63" s="179" t="n">
-        <v>0.177251735965449</v>
+        <v>0.1735189217779855</v>
       </c>
       <c r="D63" s="180" t="n">
-        <v>0.07191900920036202</v>
+        <v>0.07007619029135172</v>
       </c>
       <c r="E63" s="180" t="n">
-        <v>0.05456940615219306</v>
+        <v>0.05266413712057983</v>
       </c>
       <c r="F63" s="180" t="n">
-        <v>0.03702094949280905</v>
+        <v>0.03531044814700892</v>
       </c>
       <c r="G63" s="181" t="n">
-        <v>0.02173816878891183</v>
+        <v>0.02056933202797064</v>
       </c>
       <c r="H63" s="179" t="n">
-        <v>0.01675860125388653</v>
+        <v>0.01640567526316594</v>
       </c>
       <c r="I63" s="180" t="n">
-        <v>0.007092154897556559</v>
+        <v>0.006910428851881537</v>
       </c>
       <c r="J63" s="180" t="n">
-        <v>0.005497326260607133</v>
+        <v>0.005305389308759105</v>
       </c>
       <c r="K63" s="180" t="n">
-        <v>0.003937443090776024</v>
+        <v>0.003755519023509947</v>
       </c>
       <c r="L63" s="181" t="n">
-        <v>0.002377760234849859</v>
+        <v>0.002249910755062293</v>
       </c>
       <c r="M63" s="182" t="n">
-        <v>8326.164300336655</v>
+        <v>8150.820323826843</v>
       </c>
       <c r="N63" s="183" t="n">
-        <v>3622.764831145612</v>
+        <v>3529.936806844923</v>
       </c>
       <c r="O63" s="183" t="n">
-        <v>2859.917940121647</v>
+        <v>2760.065046925926</v>
       </c>
       <c r="P63" s="183" t="n">
-        <v>2069.46568062131</v>
+        <v>1973.848904706972</v>
       </c>
       <c r="Q63" s="184" t="n">
-        <v>1264.848019633703</v>
+        <v>1196.838571519304</v>
       </c>
       <c r="S63" s="51" t="inlineStr">
         <is>
@@ -6996,49 +6996,49 @@
         </is>
       </c>
       <c r="T63" s="185" t="n">
-        <v>0.238321540823407</v>
+        <v>0.2333026335392652</v>
       </c>
       <c r="U63" s="186" t="n">
-        <v>0.09660210570736116</v>
+        <v>0.09412681872792315</v>
       </c>
       <c r="V63" s="186" t="n">
-        <v>0.07319613015253734</v>
+        <v>0.07064051648826887</v>
       </c>
       <c r="W63" s="186" t="n">
-        <v>0.04959734741934664</v>
+        <v>0.04730577114507016</v>
       </c>
       <c r="X63" s="187" t="n">
-        <v>0.0290774565038167</v>
+        <v>0.0275139945394554</v>
       </c>
       <c r="Y63" s="185" t="n">
-        <v>0.01916201991814291</v>
+        <v>0.01875847938624739</v>
       </c>
       <c r="Z63" s="186" t="n">
-        <v>0.008112842231420631</v>
+        <v>0.007904962572953311</v>
       </c>
       <c r="AA63" s="186" t="n">
-        <v>0.006290223068369749</v>
+        <v>0.006070602441004311</v>
       </c>
       <c r="AB63" s="186" t="n">
-        <v>0.004508998075834036</v>
+        <v>0.00430066610751371</v>
       </c>
       <c r="AC63" s="187" t="n">
-        <v>0.00272462856313613</v>
+        <v>0.002578128365468683</v>
       </c>
       <c r="AD63" s="188" t="n">
-        <v>8326.164300336655</v>
+        <v>8150.820323826843</v>
       </c>
       <c r="AE63" s="189" t="n">
-        <v>3622.764831145612</v>
+        <v>3529.936806844923</v>
       </c>
       <c r="AF63" s="189" t="n">
-        <v>2859.917940121647</v>
+        <v>2760.065046925926</v>
       </c>
       <c r="AG63" s="189" t="n">
-        <v>2069.46568062131</v>
+        <v>1973.848904706972</v>
       </c>
       <c r="AH63" s="190" t="n">
-        <v>1264.848019633703</v>
+        <v>1196.838571519304</v>
       </c>
     </row>
     <row r="64" ht="15" customHeight="1" thickBot="1"/>
@@ -7297,49 +7297,49 @@
         </is>
       </c>
       <c r="C68" s="148" t="n">
-        <v>0.6338698040143969</v>
+        <v>0.6209459996405506</v>
       </c>
       <c r="D68" s="149" t="n">
-        <v>0.5926074485313441</v>
+        <v>0.57768612966128</v>
       </c>
       <c r="E68" s="149" t="n">
-        <v>0.6809529915787575</v>
+        <v>0.6575180871908062</v>
       </c>
       <c r="F68" s="149" t="n">
-        <v>0.7598414310593248</v>
+        <v>0.7251050508191268</v>
       </c>
       <c r="G68" s="150" t="n">
-        <v>0.7920665016711131</v>
+        <v>0.7498891365533319</v>
       </c>
       <c r="H68" s="148" t="n">
-        <v>0.09564004949164759</v>
+        <v>0.09369006972907327</v>
       </c>
       <c r="I68" s="149" t="n">
-        <v>0.09262392087993469</v>
+        <v>0.09029173443531562</v>
       </c>
       <c r="J68" s="149" t="n">
-        <v>0.1077012929041646</v>
+        <v>0.1039947675890821</v>
       </c>
       <c r="K68" s="149" t="n">
-        <v>0.125543551754716</v>
+        <v>0.1198042904138635</v>
       </c>
       <c r="L68" s="150" t="n">
-        <v>0.1329366538733383</v>
+        <v>0.125857806609728</v>
       </c>
       <c r="M68" s="151" t="n">
-        <v>24590.6651721253</v>
+        <v>24089.2925809487</v>
       </c>
       <c r="N68" s="152" t="n">
-        <v>24487.30537219845</v>
+        <v>23870.73719940087</v>
       </c>
       <c r="O68" s="152" t="n">
-        <v>29011.26304929479</v>
+        <v>28012.84438583071</v>
       </c>
       <c r="P68" s="152" t="n">
-        <v>34239.51953595382</v>
+        <v>32674.24957142392</v>
       </c>
       <c r="Q68" s="153" t="n">
-        <v>36814.58064506969</v>
+        <v>34854.21241052233</v>
       </c>
       <c r="S68" s="21" t="inlineStr">
         <is>
@@ -7347,49 +7347,49 @@
         </is>
       </c>
       <c r="T68" s="148" t="n">
-        <v>0.8853705384540804</v>
+        <v>0.8673189518902764</v>
       </c>
       <c r="U68" s="149" t="n">
-        <v>0.8277365043660891</v>
+        <v>0.8068948488103787</v>
       </c>
       <c r="V68" s="149" t="n">
-        <v>0.9511349381178411</v>
+        <v>0.9184017588668713</v>
       </c>
       <c r="W68" s="149" t="n">
-        <v>1.061323970153078</v>
+        <v>1.012805224690783</v>
       </c>
       <c r="X68" s="150" t="n">
-        <v>1.106334992824592</v>
+        <v>1.047422900422638</v>
       </c>
       <c r="Y68" s="148" t="n">
-        <v>0.1209185948257359</v>
+        <v>0.1184532174646577</v>
       </c>
       <c r="Z68" s="149" t="n">
-        <v>0.1171761559991153</v>
+        <v>0.114225766509472</v>
       </c>
       <c r="AA68" s="149" t="n">
-        <v>0.1362785366105418</v>
+        <v>0.1315885293485228</v>
       </c>
       <c r="AB68" s="149" t="n">
-        <v>0.1589804957170083</v>
+        <v>0.1517126543960867</v>
       </c>
       <c r="AC68" s="150" t="n">
-        <v>0.1683918572564992</v>
+        <v>0.1594250282953147</v>
       </c>
       <c r="AD68" s="151" t="n">
-        <v>24590.6651721253</v>
+        <v>24089.2925809487</v>
       </c>
       <c r="AE68" s="152" t="n">
-        <v>24487.30537219845</v>
+        <v>23870.73719940087</v>
       </c>
       <c r="AF68" s="152" t="n">
-        <v>29011.26304929479</v>
+        <v>28012.84438583071</v>
       </c>
       <c r="AG68" s="152" t="n">
-        <v>34239.51953595382</v>
+        <v>32674.24957142392</v>
       </c>
       <c r="AH68" s="153" t="n">
-        <v>36814.58064506969</v>
+        <v>34854.21241052233</v>
       </c>
     </row>
     <row r="69" ht="15" customHeight="1" thickBot="1">
@@ -7399,49 +7399,49 @@
         </is>
       </c>
       <c r="C69" s="155" t="n">
-        <v>1.373361782420405</v>
+        <v>1.341625304001562</v>
       </c>
       <c r="D69" s="156" t="n">
-        <v>1.06836198923994</v>
+        <v>1.037783435056914</v>
       </c>
       <c r="E69" s="156" t="n">
-        <v>1.224666202569629</v>
+        <v>1.177825029258079</v>
       </c>
       <c r="F69" s="156" t="n">
-        <v>1.347941943606958</v>
+        <v>1.281268373902135</v>
       </c>
       <c r="G69" s="157" t="n">
-        <v>1.48038298949741</v>
+        <v>1.395547279566251</v>
       </c>
       <c r="H69" s="155" t="n">
-        <v>0.04381499497887456</v>
+        <v>0.04280249145622802</v>
       </c>
       <c r="I69" s="156" t="n">
-        <v>0.03679308275083936</v>
+        <v>0.03573999467227761</v>
       </c>
       <c r="J69" s="156" t="n">
-        <v>0.04498423356920224</v>
+        <v>0.04326367144665733</v>
       </c>
       <c r="K69" s="156" t="n">
-        <v>0.05442633610138456</v>
+        <v>0.0517342334251198</v>
       </c>
       <c r="L69" s="157" t="n">
-        <v>0.06395932865333598</v>
+        <v>0.06029403724461195</v>
       </c>
       <c r="M69" s="158" t="n">
-        <v>10317.50320865422</v>
+        <v>10079.08007637459</v>
       </c>
       <c r="N69" s="159" t="n">
-        <v>8906.692573914248</v>
+        <v>8651.766075025278</v>
       </c>
       <c r="O69" s="159" t="n">
-        <v>11083.10567635504</v>
+        <v>10659.19777987918</v>
       </c>
       <c r="P69" s="159" t="n">
-        <v>13512.93341828743</v>
+        <v>12844.5400112465</v>
       </c>
       <c r="Q69" s="160" t="n">
-        <v>16011.70530413038</v>
+        <v>15094.12897670611</v>
       </c>
       <c r="S69" s="32" t="inlineStr">
         <is>
@@ -7449,49 +7449,49 @@
         </is>
       </c>
       <c r="T69" s="155" t="n">
-        <v>1.61277927927533</v>
+        <v>1.575510195887212</v>
       </c>
       <c r="U69" s="156" t="n">
-        <v>1.254609019318191</v>
+        <v>1.218699720539199</v>
       </c>
       <c r="V69" s="156" t="n">
-        <v>1.438161670737747</v>
+        <v>1.383154698284595</v>
       </c>
       <c r="W69" s="156" t="n">
-        <v>1.582928012227113</v>
+        <v>1.504631271286974</v>
       </c>
       <c r="X69" s="157" t="n">
-        <v>1.738457441742203</v>
+        <v>1.638832363433666</v>
       </c>
       <c r="Y69" s="155" t="n">
-        <v>0.04547785611984494</v>
+        <v>0.04442692619172428</v>
       </c>
       <c r="Z69" s="156" t="n">
-        <v>0.03820106746352653</v>
+        <v>0.03710768018183007</v>
       </c>
       <c r="AA69" s="156" t="n">
-        <v>0.0467185292875782</v>
+        <v>0.04493163362357728</v>
       </c>
       <c r="AB69" s="156" t="n">
-        <v>0.0565494013555404</v>
+        <v>0.05375228500277259</v>
       </c>
       <c r="AC69" s="157" t="n">
-        <v>0.06647682606191459</v>
+        <v>0.0626672654462206</v>
       </c>
       <c r="AD69" s="158" t="n">
-        <v>10317.50320865422</v>
+        <v>10079.08007637459</v>
       </c>
       <c r="AE69" s="159" t="n">
-        <v>8906.692573914248</v>
+        <v>8651.766075025278</v>
       </c>
       <c r="AF69" s="159" t="n">
-        <v>11083.10567635504</v>
+        <v>10659.19777987918</v>
       </c>
       <c r="AG69" s="159" t="n">
-        <v>13512.93341828743</v>
+        <v>12844.5400112465</v>
       </c>
       <c r="AH69" s="160" t="n">
-        <v>16011.70530413038</v>
+        <v>15094.12897670611</v>
       </c>
     </row>
     <row r="70" ht="15" customHeight="1" thickTop="1">
@@ -7501,49 +7501,49 @@
         </is>
       </c>
       <c r="C70" s="161" t="n">
-        <v>0.7538406142947766</v>
+        <v>0.7378647528133143</v>
       </c>
       <c r="D70" s="162" t="n">
-        <v>0.6724788260503036</v>
+        <v>0.6549289143964014</v>
       </c>
       <c r="E70" s="162" t="n">
-        <v>0.7762131358816732</v>
+        <v>0.7486773847418258</v>
       </c>
       <c r="F70" s="162" t="n">
-        <v>0.8668667883910289</v>
+        <v>0.8263183249410837</v>
       </c>
       <c r="G70" s="163" t="n">
-        <v>0.9220039655514829</v>
+        <v>0.8717737392333417</v>
       </c>
       <c r="H70" s="161" t="n">
-        <v>0.0708657687584832</v>
+        <v>0.06936393709275107</v>
       </c>
       <c r="I70" s="162" t="n">
-        <v>0.06593758038602583</v>
+        <v>0.06421678462916396</v>
       </c>
       <c r="J70" s="162" t="n">
-        <v>0.07774062535513027</v>
+        <v>0.07498281771921143</v>
       </c>
       <c r="K70" s="162" t="n">
-        <v>0.09165370398802476</v>
+        <v>0.08736652063300376</v>
       </c>
       <c r="L70" s="163" t="n">
-        <v>0.1001873056814667</v>
+        <v>0.09472916100247417</v>
       </c>
       <c r="M70" s="164" t="n">
-        <v>34908.16838077952</v>
+        <v>34168.37265732329</v>
       </c>
       <c r="N70" s="165" t="n">
-        <v>33393.9979461127</v>
+        <v>32522.50327442615</v>
       </c>
       <c r="O70" s="165" t="n">
-        <v>40094.36872564983</v>
+        <v>38672.04216570989</v>
       </c>
       <c r="P70" s="165" t="n">
-        <v>47752.45295424125</v>
+        <v>45518.78958267042</v>
       </c>
       <c r="Q70" s="166" t="n">
-        <v>52826.28594920007</v>
+        <v>49948.34138722844</v>
       </c>
       <c r="S70" s="42" t="inlineStr">
         <is>
@@ -7551,49 +7551,49 @@
         </is>
       </c>
       <c r="T70" s="161" t="n">
-        <v>1.021549691138984</v>
+        <v>0.999900371571167</v>
       </c>
       <c r="U70" s="162" t="n">
-        <v>0.9103490023468607</v>
+        <v>0.8865913107341135</v>
       </c>
       <c r="V70" s="162" t="n">
-        <v>1.049366332943908</v>
+        <v>1.012140616368451</v>
       </c>
       <c r="W70" s="162" t="n">
-        <v>1.170466141673788</v>
+        <v>1.11571654900206</v>
       </c>
       <c r="X70" s="163" t="n">
-        <v>1.243367701599066</v>
+        <v>1.175629770547292</v>
       </c>
       <c r="Y70" s="161" t="n">
-        <v>0.08113759893871228</v>
+        <v>0.07941808022745799</v>
       </c>
       <c r="Z70" s="162" t="n">
-        <v>0.07552955297146763</v>
+        <v>0.07355843220073154</v>
       </c>
       <c r="AA70" s="162" t="n">
-        <v>0.08907611218597059</v>
+        <v>0.08591618414008408</v>
       </c>
       <c r="AB70" s="162" t="n">
-        <v>0.1051058324530207</v>
+        <v>0.1001894138490645</v>
       </c>
       <c r="AC70" s="163" t="n">
-        <v>0.1149682342059774</v>
+        <v>0.1087048333537813</v>
       </c>
       <c r="AD70" s="164" t="n">
-        <v>34908.16838077952</v>
+        <v>34168.37265732329</v>
       </c>
       <c r="AE70" s="165" t="n">
-        <v>33393.9979461127</v>
+        <v>32522.50327442615</v>
       </c>
       <c r="AF70" s="165" t="n">
-        <v>40094.36872564983</v>
+        <v>38672.04216570989</v>
       </c>
       <c r="AG70" s="165" t="n">
-        <v>47752.45295424125</v>
+        <v>45518.78958267042</v>
       </c>
       <c r="AH70" s="166" t="n">
-        <v>52826.28594920007</v>
+        <v>49948.34138722844</v>
       </c>
     </row>
     <row r="71" ht="15" customHeight="1" thickBot="1">
@@ -7603,49 +7603,49 @@
         </is>
       </c>
       <c r="C71" s="155" t="n">
-        <v>3.022168676982766</v>
+        <v>2.968427503581216</v>
       </c>
       <c r="D71" s="156" t="n">
-        <v>3.693837158925251</v>
+        <v>3.614272403495752</v>
       </c>
       <c r="E71" s="156" t="n">
-        <v>4.4286243840349</v>
+        <v>4.296400954644196</v>
       </c>
       <c r="F71" s="156" t="n">
-        <v>4.864024318298085</v>
+        <v>4.661800575887735</v>
       </c>
       <c r="G71" s="157" t="n">
-        <v>5.29896045022315</v>
+        <v>5.019078991698625</v>
       </c>
       <c r="H71" s="155" t="n">
-        <v>0.1357010599458483</v>
+        <v>0.1332879801436299</v>
       </c>
       <c r="I71" s="156" t="n">
-        <v>0.1763022463350242</v>
+        <v>0.1725047196689058</v>
       </c>
       <c r="J71" s="156" t="n">
-        <v>0.2255655873251499</v>
+        <v>0.2188309779019217</v>
       </c>
       <c r="K71" s="156" t="n">
-        <v>0.2778226593323569</v>
+        <v>0.2662720719544872</v>
       </c>
       <c r="L71" s="157" t="n">
-        <v>0.3379377300221568</v>
+        <v>0.320088473425972</v>
       </c>
       <c r="M71" s="158" t="n">
-        <v>506.550214097861</v>
+        <v>497.5425756097262</v>
       </c>
       <c r="N71" s="159" t="n">
-        <v>675.2292778471705</v>
+        <v>660.684930048585</v>
       </c>
       <c r="O71" s="159" t="n">
-        <v>878.399907097712</v>
+        <v>852.1739195175425</v>
       </c>
       <c r="P71" s="159" t="n">
-        <v>1093.10737125454</v>
+        <v>1047.660998250225</v>
       </c>
       <c r="Q71" s="160" t="n">
-        <v>1345.541505725756</v>
+        <v>1274.472449320183</v>
       </c>
       <c r="S71" s="32" t="inlineStr">
         <is>
@@ -7653,49 +7653,49 @@
         </is>
       </c>
       <c r="T71" s="155" t="n">
-        <v>3.279967785556725</v>
+        <v>3.221642345663977</v>
       </c>
       <c r="U71" s="156" t="n">
-        <v>4.008931393751021</v>
+        <v>3.92257955089657</v>
       </c>
       <c r="V71" s="156" t="n">
-        <v>4.806397943501781</v>
+        <v>4.662895500305816</v>
       </c>
       <c r="W71" s="156" t="n">
-        <v>5.278938662057083</v>
+        <v>5.059464691053296</v>
       </c>
       <c r="X71" s="157" t="n">
-        <v>5.750976014688606</v>
+        <v>5.447219915723418</v>
       </c>
       <c r="Y71" s="155" t="n">
-        <v>0.1381227036330693</v>
+        <v>0.1356665613855603</v>
       </c>
       <c r="Z71" s="156" t="n">
-        <v>0.1794814540004451</v>
+        <v>0.1756154476289484</v>
       </c>
       <c r="AA71" s="156" t="n">
-        <v>0.2296810577273997</v>
+        <v>0.2228235745711669</v>
       </c>
       <c r="AB71" s="156" t="n">
-        <v>0.2830055086747527</v>
+        <v>0.2712394422774987</v>
       </c>
       <c r="AC71" s="157" t="n">
-        <v>0.3443913449647574</v>
+        <v>0.326201220158693</v>
       </c>
       <c r="AD71" s="158" t="n">
-        <v>506.550214097861</v>
+        <v>497.5425756097262</v>
       </c>
       <c r="AE71" s="159" t="n">
-        <v>675.2292778471705</v>
+        <v>660.684930048585</v>
       </c>
       <c r="AF71" s="159" t="n">
-        <v>878.399907097712</v>
+        <v>852.1739195175425</v>
       </c>
       <c r="AG71" s="159" t="n">
-        <v>1093.10737125454</v>
+        <v>1047.660998250225</v>
       </c>
       <c r="AH71" s="160" t="n">
-        <v>1345.541505725756</v>
+        <v>1274.472449320183</v>
       </c>
     </row>
     <row r="72" ht="15" customHeight="1" thickTop="1">
@@ -7705,49 +7705,49 @@
         </is>
       </c>
       <c r="C72" s="161" t="n">
-        <v>0.7620213623938417</v>
+        <v>0.7459092999329963</v>
       </c>
       <c r="D72" s="162" t="n">
-        <v>0.6835601125794</v>
+        <v>0.6657827521500721</v>
       </c>
       <c r="E72" s="162" t="n">
-        <v>0.7901844177888573</v>
+        <v>0.762248213094994</v>
       </c>
       <c r="F72" s="162" t="n">
-        <v>0.883107567521359</v>
+        <v>0.8419022041427059</v>
       </c>
       <c r="G72" s="163" t="n">
-        <v>0.9413165709678332</v>
+        <v>0.8900730461061689</v>
       </c>
       <c r="H72" s="161" t="n">
-        <v>0.071353388789423</v>
+        <v>0.06984470371351303</v>
       </c>
       <c r="I72" s="162" t="n">
-        <v>0.06676593466998378</v>
+        <v>0.06502955177814061</v>
       </c>
       <c r="J72" s="162" t="n">
-        <v>0.07884843458096619</v>
+        <v>0.07606082455138807</v>
       </c>
       <c r="K72" s="162" t="n">
-        <v>0.09304907398347573</v>
+        <v>0.08870745010146368</v>
       </c>
       <c r="L72" s="163" t="n">
-        <v>0.1019691803714561</v>
+        <v>0.09641816768279619</v>
       </c>
       <c r="M72" s="164" t="n">
-        <v>35414.71859487738</v>
+        <v>34665.91523293302</v>
       </c>
       <c r="N72" s="165" t="n">
-        <v>34069.22722395988</v>
+        <v>33183.18820447473</v>
       </c>
       <c r="O72" s="165" t="n">
-        <v>40972.76863274754</v>
+        <v>39524.21608522744</v>
       </c>
       <c r="P72" s="165" t="n">
-        <v>48845.56032549578</v>
+        <v>46566.45058092065</v>
       </c>
       <c r="Q72" s="166" t="n">
-        <v>54171.82745492583</v>
+        <v>51222.81383654862</v>
       </c>
       <c r="S72" s="42" t="inlineStr">
         <is>
@@ -7755,49 +7755,49 @@
         </is>
       </c>
       <c r="T72" s="161" t="n">
-        <v>1.031710571907087</v>
+        <v>1.009896242287952</v>
       </c>
       <c r="U72" s="162" t="n">
-        <v>0.9245113633394207</v>
+        <v>0.9004675792966748</v>
       </c>
       <c r="V72" s="162" t="n">
-        <v>1.067251326879239</v>
+        <v>1.029519689990061</v>
       </c>
       <c r="W72" s="162" t="n">
-        <v>1.191213417185956</v>
+        <v>1.135631986880199</v>
       </c>
       <c r="X72" s="163" t="n">
-        <v>1.268054579790852</v>
+        <v>1.199024044910701</v>
       </c>
       <c r="Y72" s="161" t="n">
-        <v>0.08161924449549263</v>
+        <v>0.07989349974578215</v>
       </c>
       <c r="Z72" s="162" t="n">
-        <v>0.07640662008633925</v>
+        <v>0.07441951171142833</v>
       </c>
       <c r="AA72" s="162" t="n">
-        <v>0.09026071056769258</v>
+        <v>0.08706963057488719</v>
       </c>
       <c r="AB72" s="162" t="n">
-        <v>0.1066055091539175</v>
+        <v>0.1016313486955459</v>
       </c>
       <c r="AC72" s="163" t="n">
-        <v>0.1169025733448186</v>
+        <v>0.1105386144936231</v>
       </c>
       <c r="AD72" s="164" t="n">
-        <v>35414.71859487738</v>
+        <v>34665.91523293302</v>
       </c>
       <c r="AE72" s="165" t="n">
-        <v>34069.22722395988</v>
+        <v>33183.18820447473</v>
       </c>
       <c r="AF72" s="165" t="n">
-        <v>40972.76863274754</v>
+        <v>39524.21608522744</v>
       </c>
       <c r="AG72" s="165" t="n">
-        <v>48845.56032549578</v>
+        <v>46566.45058092065</v>
       </c>
       <c r="AH72" s="166" t="n">
-        <v>54171.82745492583</v>
+        <v>51222.81383654862</v>
       </c>
     </row>
     <row r="73" ht="15" customHeight="1" thickBot="1">
@@ -7807,49 +7807,49 @@
         </is>
       </c>
       <c r="C73" s="155" t="n">
-        <v>16.27687319072329</v>
+        <v>16.27687319072328</v>
       </c>
       <c r="D73" s="156" t="n">
-        <v>25.7563301850302</v>
+        <v>25.75633018503019</v>
       </c>
       <c r="E73" s="156" t="n">
-        <v>39.11906585717956</v>
+        <v>38.83906009929751</v>
       </c>
       <c r="F73" s="156" t="n">
-        <v>56.79460845809642</v>
+        <v>55.98440123228492</v>
       </c>
       <c r="G73" s="157" t="n">
-        <v>77.39076478310314</v>
+        <v>75.7375039024531</v>
       </c>
       <c r="H73" s="155" t="n">
         <v>16.21600084936059</v>
       </c>
       <c r="I73" s="156" t="n">
-        <v>25.63979427407406</v>
+        <v>25.63979427407405</v>
       </c>
       <c r="J73" s="156" t="n">
-        <v>36.3907187918691</v>
+        <v>36.130241948368</v>
       </c>
       <c r="K73" s="156" t="n">
-        <v>52.08484378882883</v>
+        <v>51.34182402095583</v>
       </c>
       <c r="L73" s="157" t="n">
-        <v>71.14323992193721</v>
+        <v>69.62344184505713</v>
       </c>
       <c r="M73" s="158" t="n">
-        <v>8121.5546470215</v>
+        <v>8121.554647021499</v>
       </c>
       <c r="N73" s="159" t="n">
-        <v>13701.75767699508</v>
+        <v>13701.75767699507</v>
       </c>
       <c r="O73" s="159" t="n">
-        <v>21775.85527117035</v>
+        <v>21619.98843935501</v>
       </c>
       <c r="P73" s="159" t="n">
-        <v>33443.8968235424</v>
+        <v>32966.80071175707</v>
       </c>
       <c r="Q73" s="160" t="n">
-        <v>49265.61924720133</v>
+        <v>48213.18203081423</v>
       </c>
       <c r="S73" s="32" t="inlineStr">
         <is>
@@ -7860,46 +7860,46 @@
         <v>13.30379437087634</v>
       </c>
       <c r="U73" s="156" t="n">
-        <v>21.05176568711786</v>
+        <v>21.05176568711785</v>
       </c>
       <c r="V73" s="156" t="n">
-        <v>31.9737090807648</v>
+        <v>31.74484823127147</v>
       </c>
       <c r="W73" s="156" t="n">
-        <v>46.42069661951907</v>
+        <v>45.758479115967</v>
       </c>
       <c r="X73" s="157" t="n">
-        <v>63.25482841913761</v>
+        <v>61.90354660107212</v>
       </c>
       <c r="Y73" s="155" t="n">
         <v>13.26310079430229</v>
       </c>
       <c r="Z73" s="156" t="n">
-        <v>20.97384945741587</v>
+        <v>20.97384945741586</v>
       </c>
       <c r="AA73" s="156" t="n">
-        <v>30.12751707590271</v>
+        <v>29.91187086689707</v>
       </c>
       <c r="AB73" s="156" t="n">
-        <v>43.22594648865292</v>
+        <v>42.6093039034067</v>
       </c>
       <c r="AC73" s="157" t="n">
-        <v>59.01870528816365</v>
+        <v>57.75791768704619</v>
       </c>
       <c r="AD73" s="158" t="n">
-        <v>8121.5546470215</v>
+        <v>8121.554647021499</v>
       </c>
       <c r="AE73" s="159" t="n">
-        <v>13701.75767699508</v>
+        <v>13701.75767699507</v>
       </c>
       <c r="AF73" s="159" t="n">
-        <v>21775.85527117035</v>
+        <v>21619.98843935501</v>
       </c>
       <c r="AG73" s="159" t="n">
-        <v>33443.8968235424</v>
+        <v>32966.80071175707</v>
       </c>
       <c r="AH73" s="160" t="n">
-        <v>49265.61924720133</v>
+        <v>48213.18203081423</v>
       </c>
     </row>
     <row r="74" ht="15.6" customHeight="1" thickBot="1" thickTop="1">
@@ -7909,49 +7909,49 @@
         </is>
       </c>
       <c r="C74" s="179" t="n">
-        <v>0.9268229320529605</v>
+        <v>0.9108820148414136</v>
       </c>
       <c r="D74" s="180" t="n">
-        <v>0.9483480332659893</v>
+        <v>0.9307584155667138</v>
       </c>
       <c r="E74" s="180" t="n">
-        <v>1.197291396115532</v>
+        <v>1.166677855943229</v>
       </c>
       <c r="F74" s="180" t="n">
-        <v>1.472087150529887</v>
+        <v>1.422781013803101</v>
       </c>
       <c r="G74" s="181" t="n">
-        <v>1.777716089681734</v>
+        <v>1.708945603191326</v>
       </c>
       <c r="H74" s="179" t="n">
-        <v>0.08762823036193663</v>
+        <v>0.08612106613748242</v>
       </c>
       <c r="I74" s="180" t="n">
-        <v>0.09351951901864715</v>
+        <v>0.09178495266826094</v>
       </c>
       <c r="J74" s="180" t="n">
-        <v>0.120615229256996</v>
+        <v>0.1175312188162375</v>
       </c>
       <c r="K74" s="180" t="n">
-        <v>0.1565670102815687</v>
+        <v>0.151322949552509</v>
       </c>
       <c r="L74" s="181" t="n">
-        <v>0.1944498024623907</v>
+        <v>0.1869275622177764</v>
       </c>
       <c r="M74" s="182" t="n">
-        <v>43536.27324189888</v>
+        <v>42787.46987995451</v>
       </c>
       <c r="N74" s="183" t="n">
-        <v>47770.98490095495</v>
+        <v>46884.94588146981</v>
       </c>
       <c r="O74" s="183" t="n">
-        <v>62748.62390391788</v>
+        <v>61144.20452458246</v>
       </c>
       <c r="P74" s="183" t="n">
-        <v>82289.45714903819</v>
+        <v>79533.25129267771</v>
       </c>
       <c r="Q74" s="184" t="n">
-        <v>103437.4467021272</v>
+        <v>99435.99586736286</v>
       </c>
       <c r="S74" s="51" t="inlineStr">
         <is>
@@ -7959,49 +7959,49 @@
         </is>
       </c>
       <c r="T74" s="185" t="n">
-        <v>1.246147847490673</v>
+        <v>1.224714692372041</v>
       </c>
       <c r="U74" s="186" t="n">
-        <v>1.273827573203942</v>
+        <v>1.250201078244819</v>
       </c>
       <c r="V74" s="186" t="n">
-        <v>1.605974904989206</v>
+        <v>1.564911737385141</v>
       </c>
       <c r="W74" s="186" t="n">
-        <v>1.972170320768478</v>
+        <v>1.906114381451762</v>
       </c>
       <c r="X74" s="187" t="n">
-        <v>2.377912453243183</v>
+        <v>2.285923525882791</v>
       </c>
       <c r="Y74" s="185" t="n">
-        <v>0.1001953486540312</v>
+        <v>0.09847203592336957</v>
       </c>
       <c r="Z74" s="186" t="n">
-        <v>0.1069786425022981</v>
+        <v>0.1049944411778935</v>
       </c>
       <c r="AA74" s="186" t="n">
-        <v>0.1380119464449015</v>
+        <v>0.1344831193937288</v>
       </c>
       <c r="AB74" s="186" t="n">
-        <v>0.1792941083396191</v>
+        <v>0.173288825420793</v>
       </c>
       <c r="AC74" s="187" t="n">
-        <v>0.2228161940468575</v>
+        <v>0.2141966072908605</v>
       </c>
       <c r="AD74" s="188" t="n">
-        <v>43536.27324189888</v>
+        <v>42787.46987995451</v>
       </c>
       <c r="AE74" s="189" t="n">
-        <v>47770.98490095495</v>
+        <v>46884.94588146981</v>
       </c>
       <c r="AF74" s="189" t="n">
-        <v>62748.62390391788</v>
+        <v>61144.20452458246</v>
       </c>
       <c r="AG74" s="189" t="n">
-        <v>82289.45714903819</v>
+        <v>79533.25129267771</v>
       </c>
       <c r="AH74" s="190" t="n">
-        <v>103437.4467021272</v>
+        <v>99435.99586736286</v>
       </c>
     </row>
     <row r="75" ht="15" customHeight="1" thickBot="1"/>
@@ -8260,49 +8260,49 @@
         </is>
       </c>
       <c r="C79" s="148" t="n">
-        <v>253.2437750495938</v>
+        <v>258.1069815352852</v>
       </c>
       <c r="D79" s="149" t="n">
-        <v>284.9745748049519</v>
+        <v>291.1806136466871</v>
       </c>
       <c r="E79" s="149" t="n">
-        <v>314.7381730030974</v>
+        <v>323.5908559494646</v>
       </c>
       <c r="F79" s="149" t="n">
-        <v>347.7581392889213</v>
+        <v>359.9134272336371</v>
       </c>
       <c r="G79" s="150" t="n">
-        <v>375.5416178571007</v>
+        <v>390.3501826086383</v>
       </c>
       <c r="H79" s="148" t="n">
-        <v>38.21012931331354</v>
+        <v>38.94390351431503</v>
       </c>
       <c r="I79" s="149" t="n">
-        <v>44.54122629565766</v>
+        <v>45.51122363888931</v>
       </c>
       <c r="J79" s="149" t="n">
-        <v>49.77980650343861</v>
+        <v>51.17996981982831</v>
       </c>
       <c r="K79" s="149" t="n">
-        <v>57.45776707263247</v>
+        <v>59.46610454779939</v>
       </c>
       <c r="L79" s="150" t="n">
-        <v>63.02910925127384</v>
+        <v>65.51450794264974</v>
       </c>
       <c r="M79" s="151" t="n">
-        <v>9824466.853808574</v>
+        <v>10013132.54129703</v>
       </c>
       <c r="N79" s="152" t="n">
-        <v>11775517.5940759</v>
+        <v>12031959.13669559</v>
       </c>
       <c r="O79" s="152" t="n">
-        <v>13409078.22062376</v>
+        <v>13786237.16819461</v>
       </c>
       <c r="P79" s="152" t="n">
-        <v>15670469.01795004</v>
+        <v>16218203.32413023</v>
       </c>
       <c r="Q79" s="153" t="n">
-        <v>17454856.56445657</v>
+        <v>18143146.12112006</v>
       </c>
       <c r="S79" s="21" t="inlineStr">
         <is>
@@ -8310,49 +8310,49 @@
         </is>
       </c>
       <c r="T79" s="148" t="n">
-        <v>353.7233924945103</v>
+        <v>360.5161750463548</v>
       </c>
       <c r="U79" s="149" t="n">
-        <v>398.0440322963425</v>
+        <v>406.7124432478906</v>
       </c>
       <c r="V79" s="149" t="n">
-        <v>439.6169433202354</v>
+        <v>451.9821082442461</v>
       </c>
       <c r="W79" s="149" t="n">
-        <v>485.7382526886045</v>
+        <v>502.7163983022942</v>
       </c>
       <c r="X79" s="150" t="n">
-        <v>524.5453913537518</v>
+        <v>545.2295553015633</v>
       </c>
       <c r="Y79" s="148" t="n">
-        <v>48.30941816983307</v>
+        <v>49.23713564568219</v>
       </c>
       <c r="Z79" s="149" t="n">
-        <v>56.34796747135454</v>
+        <v>57.57508632930672</v>
       </c>
       <c r="AA79" s="149" t="n">
-        <v>62.98827990004779</v>
+        <v>64.75995972512789</v>
       </c>
       <c r="AB79" s="149" t="n">
-        <v>72.76091973123879</v>
+        <v>75.30415260068074</v>
       </c>
       <c r="AC79" s="150" t="n">
-        <v>79.83944577209988</v>
+        <v>82.98771894935635</v>
       </c>
       <c r="AD79" s="151" t="n">
-        <v>9824466.853808574</v>
+        <v>10013132.54129703</v>
       </c>
       <c r="AE79" s="152" t="n">
-        <v>11775517.5940759</v>
+        <v>12031959.13669559</v>
       </c>
       <c r="AF79" s="152" t="n">
-        <v>13409078.22062376</v>
+        <v>13786237.16819461</v>
       </c>
       <c r="AG79" s="152" t="n">
-        <v>15670469.01795004</v>
+        <v>16218203.32413023</v>
       </c>
       <c r="AH79" s="153" t="n">
-        <v>17454856.56445657</v>
+        <v>18143146.12112006</v>
       </c>
     </row>
     <row r="80" ht="15" customHeight="1" thickBot="1">
@@ -8362,49 +8362,49 @@
         </is>
       </c>
       <c r="C80" s="155" t="n">
-        <v>670.1265031122902</v>
+        <v>685.0805041737755</v>
       </c>
       <c r="D80" s="156" t="n">
-        <v>738.3893105236601</v>
+        <v>757.2626985526653</v>
       </c>
       <c r="E80" s="156" t="n">
-        <v>799.0972238838543</v>
+        <v>825.1200605751549</v>
       </c>
       <c r="F80" s="156" t="n">
-        <v>858.2878462863857</v>
+        <v>892.4186779377792</v>
       </c>
       <c r="G80" s="157" t="n">
-        <v>906.895214309991</v>
+        <v>947.7640657683435</v>
       </c>
       <c r="H80" s="155" t="n">
-        <v>21.37935520335294</v>
+        <v>21.85643960297001</v>
       </c>
       <c r="I80" s="156" t="n">
-        <v>25.42922649631142</v>
+        <v>26.07920294112476</v>
       </c>
       <c r="J80" s="156" t="n">
-        <v>29.35230521448855</v>
+        <v>30.3081716876536</v>
       </c>
       <c r="K80" s="156" t="n">
-        <v>34.65539670700931</v>
+        <v>36.03350955800327</v>
       </c>
       <c r="L80" s="157" t="n">
-        <v>39.18202889232251</v>
+        <v>40.94775054722789</v>
       </c>
       <c r="M80" s="158" t="n">
-        <v>5034385.283300975</v>
+        <v>5146728.553595112</v>
       </c>
       <c r="N80" s="159" t="n">
-        <v>6155784.88839491</v>
+        <v>6313128.061116857</v>
       </c>
       <c r="O80" s="159" t="n">
-        <v>7231749.320266849</v>
+        <v>7467253.368997071</v>
       </c>
       <c r="P80" s="159" t="n">
-        <v>8604218.138325889</v>
+        <v>8946375.052281627</v>
       </c>
       <c r="Q80" s="160" t="n">
-        <v>9808906.895226894</v>
+        <v>10250941.15954358</v>
       </c>
       <c r="S80" s="32" t="inlineStr">
         <is>
@@ -8412,49 +8412,49 @@
         </is>
       </c>
       <c r="T80" s="155" t="n">
-        <v>786.9493330504654</v>
+        <v>804.5102579013959</v>
       </c>
       <c r="U80" s="156" t="n">
-        <v>867.1123627396947</v>
+        <v>889.2759393970106</v>
       </c>
       <c r="V80" s="156" t="n">
-        <v>938.4034573431937</v>
+        <v>968.9628425983515</v>
       </c>
       <c r="W80" s="156" t="n">
-        <v>1007.912752388504</v>
+        <v>1047.993595452878</v>
       </c>
       <c r="X80" s="157" t="n">
-        <v>1064.99381942564</v>
+        <v>1112.987318038692</v>
       </c>
       <c r="Y80" s="155" t="n">
-        <v>22.19074178467742</v>
+        <v>22.68593243101365</v>
       </c>
       <c r="Z80" s="156" t="n">
-        <v>26.40234316622267</v>
+        <v>27.07719268035998</v>
       </c>
       <c r="AA80" s="156" t="n">
-        <v>30.4839367488936</v>
+        <v>31.47665513661221</v>
       </c>
       <c r="AB80" s="156" t="n">
-        <v>36.00723616356547</v>
+        <v>37.43910650991609</v>
       </c>
       <c r="AC80" s="157" t="n">
-        <v>40.72426922342282</v>
+        <v>42.5594912902945</v>
       </c>
       <c r="AD80" s="158" t="n">
-        <v>5034385.283300975</v>
+        <v>5146728.553595112</v>
       </c>
       <c r="AE80" s="159" t="n">
-        <v>6155784.88839491</v>
+        <v>6313128.061116857</v>
       </c>
       <c r="AF80" s="159" t="n">
-        <v>7231749.320266849</v>
+        <v>7467253.368997071</v>
       </c>
       <c r="AG80" s="159" t="n">
-        <v>8604218.138325889</v>
+        <v>8946375.052281627</v>
       </c>
       <c r="AH80" s="160" t="n">
-        <v>9808906.895226894</v>
+        <v>10250941.15954358</v>
       </c>
     </row>
     <row r="81" ht="15" customHeight="1" thickTop="1">
@@ -8464,49 +8464,49 @@
         </is>
       </c>
       <c r="C81" s="161" t="n">
-        <v>320.8763662581997</v>
+        <v>327.3766436479466</v>
       </c>
       <c r="D81" s="162" t="n">
-        <v>361.0954657906886</v>
+        <v>369.4281446169713</v>
       </c>
       <c r="E81" s="162" t="n">
-        <v>399.5992949119024</v>
+        <v>411.4602389973815</v>
       </c>
       <c r="F81" s="162" t="n">
-        <v>440.6667886678457</v>
+        <v>456.8212916575836</v>
       </c>
       <c r="G81" s="163" t="n">
-        <v>475.8482935911646</v>
+        <v>495.5764086114637</v>
       </c>
       <c r="H81" s="161" t="n">
-        <v>30.16440072360466</v>
+        <v>30.77546776567262</v>
       </c>
       <c r="I81" s="162" t="n">
-        <v>35.40596429250535</v>
+        <v>36.22299623262752</v>
       </c>
       <c r="J81" s="162" t="n">
-        <v>40.02135192241325</v>
+        <v>41.2092694773771</v>
       </c>
       <c r="K81" s="162" t="n">
-        <v>46.59163777733462</v>
+        <v>48.29965111332046</v>
       </c>
       <c r="L81" s="163" t="n">
-        <v>51.70689089119793</v>
+        <v>53.85059825462083</v>
       </c>
       <c r="M81" s="164" t="n">
-        <v>14858852.13710955</v>
+        <v>15159861.09489214</v>
       </c>
       <c r="N81" s="165" t="n">
-        <v>17931302.48247081</v>
+        <v>18345087.19781244</v>
       </c>
       <c r="O81" s="165" t="n">
-        <v>20640827.54089061</v>
+        <v>21253490.53719168</v>
       </c>
       <c r="P81" s="165" t="n">
-        <v>24274687.15627593</v>
+        <v>25164578.37641186</v>
       </c>
       <c r="Q81" s="166" t="n">
-        <v>27263763.45968346</v>
+        <v>28394087.28066364</v>
       </c>
       <c r="S81" s="42" t="inlineStr">
         <is>
@@ -8514,49 +8514,49 @@
         </is>
       </c>
       <c r="T81" s="161" t="n">
-        <v>434.8281939565094</v>
+        <v>443.636894673737</v>
       </c>
       <c r="U81" s="162" t="n">
-        <v>488.822672626333</v>
+        <v>500.1027985760768</v>
       </c>
       <c r="V81" s="162" t="n">
-        <v>540.2202402467415</v>
+        <v>556.255108538547</v>
       </c>
       <c r="W81" s="162" t="n">
-        <v>594.9997886678406</v>
+        <v>616.8120198413885</v>
       </c>
       <c r="X81" s="163" t="n">
-        <v>641.7048312350746</v>
+        <v>668.3091647804291</v>
       </c>
       <c r="Y81" s="161" t="n">
-        <v>34.53666122609383</v>
+        <v>35.23630103036872</v>
       </c>
       <c r="Z81" s="162" t="n">
-        <v>40.55648751259635</v>
+        <v>41.49237349505979</v>
       </c>
       <c r="AA81" s="162" t="n">
-        <v>45.85693023936852</v>
+        <v>47.21805998215442</v>
       </c>
       <c r="AB81" s="162" t="n">
-        <v>53.42995057325995</v>
+        <v>55.38865115717862</v>
       </c>
       <c r="AC81" s="163" t="n">
-        <v>59.33536091830284</v>
+        <v>61.79533574795508</v>
       </c>
       <c r="AD81" s="164" t="n">
-        <v>14858852.13710955</v>
+        <v>15159861.09489214</v>
       </c>
       <c r="AE81" s="165" t="n">
-        <v>17931302.48247081</v>
+        <v>18345087.19781244</v>
       </c>
       <c r="AF81" s="165" t="n">
-        <v>20640827.54089061</v>
+        <v>21253490.53719168</v>
       </c>
       <c r="AG81" s="165" t="n">
-        <v>24274687.15627593</v>
+        <v>25164578.37641186</v>
       </c>
       <c r="AH81" s="166" t="n">
-        <v>27263763.45968346</v>
+        <v>28394087.28066364</v>
       </c>
     </row>
     <row r="82" ht="15" customHeight="1" thickBot="1">
@@ -8566,49 +8566,49 @@
         </is>
       </c>
       <c r="C82" s="155" t="n">
-        <v>879.1869016646149</v>
+        <v>893.0421521844499</v>
       </c>
       <c r="D82" s="156" t="n">
-        <v>990.9465413027943</v>
+        <v>1008.579680838801</v>
       </c>
       <c r="E82" s="156" t="n">
-        <v>1058.559681899819</v>
+        <v>1083.776695868935</v>
       </c>
       <c r="F82" s="156" t="n">
-        <v>1129.443818612265</v>
+        <v>1164.839241990578</v>
       </c>
       <c r="G82" s="157" t="n">
-        <v>1190.522332680766</v>
+        <v>1235.586250673387</v>
       </c>
       <c r="H82" s="155" t="n">
-        <v>39.47714611532083</v>
+        <v>40.09927293295232</v>
       </c>
       <c r="I82" s="156" t="n">
-        <v>47.29664403517926</v>
+        <v>48.1382518203588</v>
       </c>
       <c r="J82" s="156" t="n">
-        <v>53.9162086600151</v>
+        <v>55.20060084893849</v>
       </c>
       <c r="K82" s="156" t="n">
-        <v>64.5114137429199</v>
+        <v>66.53312457486703</v>
       </c>
       <c r="L82" s="157" t="n">
-        <v>75.92478155406469</v>
+        <v>78.79870339126008</v>
       </c>
       <c r="M82" s="158" t="n">
-        <v>147361.8321379966</v>
+        <v>149684.1314095941</v>
       </c>
       <c r="N82" s="159" t="n">
-        <v>181143.9131398313</v>
+        <v>184367.2312133711</v>
       </c>
       <c r="O82" s="159" t="n">
-        <v>209961.0726956737</v>
+        <v>214962.7664061643</v>
       </c>
       <c r="P82" s="159" t="n">
-        <v>253823.4356474041</v>
+        <v>261777.9596529598</v>
       </c>
       <c r="Q82" s="160" t="n">
-        <v>302304.0513631232</v>
+        <v>313746.9320260917</v>
       </c>
       <c r="S82" s="32" t="inlineStr">
         <is>
@@ -8616,49 +8616,49 @@
         </is>
       </c>
       <c r="T82" s="155" t="n">
-        <v>954.1839067111107</v>
+        <v>969.2210473287043</v>
       </c>
       <c r="U82" s="156" t="n">
-        <v>1075.476943903405</v>
+        <v>1094.614237621263</v>
       </c>
       <c r="V82" s="156" t="n">
-        <v>1148.857667066735</v>
+        <v>1176.225760084365</v>
       </c>
       <c r="W82" s="156" t="n">
-        <v>1225.788411103146</v>
+        <v>1264.203159201493</v>
       </c>
       <c r="X82" s="157" t="n">
-        <v>1292.077086536829</v>
+        <v>1340.985077818883</v>
       </c>
       <c r="Y82" s="155" t="n">
-        <v>40.18163273994866</v>
+        <v>40.81486167779329</v>
       </c>
       <c r="Z82" s="156" t="n">
-        <v>48.14953080429952</v>
+        <v>49.0063150604404</v>
       </c>
       <c r="AA82" s="156" t="n">
-        <v>54.8999161642186</v>
+        <v>56.20774223816441</v>
       </c>
       <c r="AB82" s="156" t="n">
-        <v>65.71488987081388</v>
+        <v>67.77431621049192</v>
       </c>
       <c r="AC82" s="157" t="n">
-        <v>77.37472117672499</v>
+        <v>80.3035264532782</v>
       </c>
       <c r="AD82" s="158" t="n">
-        <v>147361.8321379966</v>
+        <v>149684.1314095941</v>
       </c>
       <c r="AE82" s="159" t="n">
-        <v>181143.9131398313</v>
+        <v>184367.2312133711</v>
       </c>
       <c r="AF82" s="159" t="n">
-        <v>209961.0726956737</v>
+        <v>214962.7664061643</v>
       </c>
       <c r="AG82" s="159" t="n">
-        <v>253823.4356474041</v>
+        <v>261777.9596529598</v>
       </c>
       <c r="AH82" s="160" t="n">
-        <v>302304.0513631232</v>
+        <v>313746.9320260917</v>
       </c>
     </row>
     <row r="83" ht="15" customHeight="1" thickTop="1">
@@ -8668,49 +8668,49 @@
         </is>
       </c>
       <c r="C83" s="161" t="n">
-        <v>322.8899188506769</v>
+        <v>329.4167220254027</v>
       </c>
       <c r="D83" s="162" t="n">
-        <v>363.4055394295766</v>
+        <v>371.7723290956282</v>
       </c>
       <c r="E83" s="162" t="n">
-        <v>402.1199643291074</v>
+        <v>414.0319983397998</v>
       </c>
       <c r="F83" s="162" t="n">
-        <v>443.4653462752644</v>
+        <v>459.6980267038339</v>
       </c>
       <c r="G83" s="163" t="n">
-        <v>479.0016760308993</v>
+        <v>498.8415811426522</v>
       </c>
       <c r="H83" s="161" t="n">
-        <v>30.23444099199677</v>
+        <v>30.84559121358014</v>
       </c>
       <c r="I83" s="162" t="n">
-        <v>35.49521111275639</v>
+        <v>36.31242750961894</v>
       </c>
       <c r="J83" s="162" t="n">
-        <v>40.12548082108129</v>
+        <v>41.31412136280012</v>
       </c>
       <c r="K83" s="162" t="n">
-        <v>46.72594973961282</v>
+        <v>48.43631429507402</v>
       </c>
       <c r="L83" s="163" t="n">
-        <v>51.88839738708224</v>
+        <v>54.0375775091456</v>
       </c>
       <c r="M83" s="164" t="n">
-        <v>15006213.96924755</v>
+        <v>15309545.22630173</v>
       </c>
       <c r="N83" s="165" t="n">
-        <v>18112446.39561064</v>
+        <v>18529454.42902581</v>
       </c>
       <c r="O83" s="165" t="n">
-        <v>20850788.61358628</v>
+        <v>21468453.30359784</v>
       </c>
       <c r="P83" s="165" t="n">
-        <v>24528510.59192333</v>
+        <v>25426356.33606482</v>
       </c>
       <c r="Q83" s="166" t="n">
-        <v>27566067.51104658</v>
+        <v>28707834.21268973</v>
       </c>
       <c r="S83" s="42" t="inlineStr">
         <is>
@@ -8718,49 +8718,49 @@
         </is>
       </c>
       <c r="T83" s="161" t="n">
-        <v>437.1648345841136</v>
+        <v>446.001557763327</v>
       </c>
       <c r="U83" s="162" t="n">
-        <v>491.5040309115609</v>
+        <v>502.8200687823884</v>
       </c>
       <c r="V83" s="162" t="n">
-        <v>543.1176011997079</v>
+        <v>559.2064202368091</v>
       </c>
       <c r="W83" s="162" t="n">
-        <v>598.1851927991029</v>
+        <v>620.0812646192962</v>
       </c>
       <c r="X83" s="163" t="n">
-        <v>645.2667335856687</v>
+        <v>671.9932178689609</v>
       </c>
       <c r="Y83" s="161" t="n">
-        <v>34.58437326351804</v>
+        <v>35.28345175446536</v>
       </c>
       <c r="Z83" s="162" t="n">
-        <v>40.62055183953053</v>
+        <v>41.55577042176174</v>
       </c>
       <c r="AA83" s="162" t="n">
-        <v>45.93311750611979</v>
+        <v>47.29379816484535</v>
       </c>
       <c r="AB83" s="162" t="n">
-        <v>53.53351139825837</v>
+        <v>55.49306109035025</v>
       </c>
       <c r="AC83" s="163" t="n">
-        <v>59.48745649608535</v>
+        <v>61.95138418419167</v>
       </c>
       <c r="AD83" s="164" t="n">
-        <v>15006213.96924755</v>
+        <v>15309545.22630173</v>
       </c>
       <c r="AE83" s="165" t="n">
-        <v>18112446.39561064</v>
+        <v>18529454.42902581</v>
       </c>
       <c r="AF83" s="165" t="n">
-        <v>20850788.61358628</v>
+        <v>21468453.30359784</v>
       </c>
       <c r="AG83" s="165" t="n">
-        <v>24528510.59192333</v>
+        <v>25426356.33606482</v>
       </c>
       <c r="AH83" s="166" t="n">
-        <v>27566067.51104658</v>
+        <v>28707834.21268973</v>
       </c>
     </row>
     <row r="84" ht="15" customHeight="1" thickBot="1">
@@ -8770,49 +8770,49 @@
         </is>
       </c>
       <c r="C84" s="155" t="n">
-        <v>3919.434024576821</v>
+        <v>3919.434024576819</v>
       </c>
       <c r="D84" s="156" t="n">
-        <v>4369.702217990102</v>
+        <v>4369.702217990101</v>
       </c>
       <c r="E84" s="156" t="n">
-        <v>4506.775808984617</v>
+        <v>4546.301036116548</v>
       </c>
       <c r="F84" s="156" t="n">
-        <v>4996.72203479779</v>
+        <v>5081.675758765602</v>
       </c>
       <c r="G84" s="157" t="n">
-        <v>5464.905209402667</v>
+        <v>5599.966051417687</v>
       </c>
       <c r="H84" s="155" t="n">
-        <v>3904.776103298146</v>
+        <v>3904.776103298145</v>
       </c>
       <c r="I84" s="156" t="n">
-        <v>4349.931263629666</v>
+        <v>4349.931263629665</v>
       </c>
       <c r="J84" s="156" t="n">
-        <v>4192.452133737688</v>
+        <v>4229.220686212693</v>
       </c>
       <c r="K84" s="156" t="n">
-        <v>4582.362546449443</v>
+        <v>4660.271375513868</v>
       </c>
       <c r="L84" s="157" t="n">
-        <v>5023.739764722728</v>
+        <v>5147.897549110346</v>
       </c>
       <c r="M84" s="158" t="n">
-        <v>1955651.877544766</v>
+        <v>1955651.877544765</v>
       </c>
       <c r="N84" s="159" t="n">
         <v>2324578.093284686</v>
       </c>
       <c r="O84" s="159" t="n">
-        <v>2508722.936134457</v>
+        <v>2530724.883438807</v>
       </c>
       <c r="P84" s="159" t="n">
-        <v>2942354.225595081</v>
+        <v>2992379.811760562</v>
       </c>
       <c r="Q84" s="160" t="n">
-        <v>3478863.919009375</v>
+        <v>3564841.30967823</v>
       </c>
       <c r="S84" s="32" t="inlineStr">
         <is>
@@ -8820,49 +8820,49 @@
         </is>
       </c>
       <c r="T84" s="155" t="n">
-        <v>3203.523410313504</v>
+        <v>3203.523410313503</v>
       </c>
       <c r="U84" s="156" t="n">
-        <v>3571.547132482103</v>
+        <v>3571.547132482102</v>
       </c>
       <c r="V84" s="156" t="n">
-        <v>3683.583323149729</v>
+        <v>3715.889005455167</v>
       </c>
       <c r="W84" s="156" t="n">
-        <v>4084.037621996285</v>
+        <v>4153.473984955242</v>
       </c>
       <c r="X84" s="157" t="n">
-        <v>4466.704035248019</v>
+        <v>4577.095118883744</v>
       </c>
       <c r="Y84" s="155" t="n">
-        <v>3193.724489677018</v>
+        <v>3193.724489677016</v>
       </c>
       <c r="Z84" s="156" t="n">
         <v>3558.328218168599</v>
       </c>
       <c r="AA84" s="156" t="n">
-        <v>3470.889760971372</v>
+        <v>3501.330082826032</v>
       </c>
       <c r="AB84" s="156" t="n">
-        <v>3802.96730902195</v>
+        <v>3867.624945124043</v>
       </c>
       <c r="AC84" s="157" t="n">
-        <v>4167.572589383498</v>
+        <v>4270.570874168454</v>
       </c>
       <c r="AD84" s="158" t="n">
-        <v>1955651.877544766</v>
+        <v>1955651.877544765</v>
       </c>
       <c r="AE84" s="159" t="n">
         <v>2324578.093284686</v>
       </c>
       <c r="AF84" s="159" t="n">
-        <v>2508722.936134457</v>
+        <v>2530724.883438807</v>
       </c>
       <c r="AG84" s="159" t="n">
-        <v>2942354.225595081</v>
+        <v>2992379.811760562</v>
       </c>
       <c r="AH84" s="160" t="n">
-        <v>3478863.919009375</v>
+        <v>3564841.30967823</v>
       </c>
     </row>
     <row r="85" ht="15.6" customHeight="1" thickBot="1" thickTop="1">
@@ -8872,49 +8872,49 @@
         </is>
       </c>
       <c r="C85" s="179" t="n">
-        <v>361.0930625564805</v>
+        <v>367.5505368442822</v>
       </c>
       <c r="D85" s="180" t="n">
-        <v>405.7151431990949</v>
+        <v>413.9935730695558</v>
       </c>
       <c r="E85" s="180" t="n">
-        <v>445.7172198511876</v>
+        <v>457.9225450613978</v>
       </c>
       <c r="F85" s="180" t="n">
-        <v>491.4299900966727</v>
+        <v>508.3865876249973</v>
       </c>
       <c r="G85" s="181" t="n">
-        <v>533.5502360688267</v>
+        <v>554.6507223675653</v>
       </c>
       <c r="H85" s="179" t="n">
-        <v>34.1402278401851</v>
+        <v>34.75076198309239</v>
       </c>
       <c r="I85" s="180" t="n">
-        <v>40.00881925161223</v>
+        <v>40.82518070601297</v>
       </c>
       <c r="J85" s="180" t="n">
-        <v>44.90158772589582</v>
+        <v>46.13115314594471</v>
       </c>
       <c r="K85" s="180" t="n">
-        <v>52.26709864592003</v>
+        <v>54.07055422163236</v>
       </c>
       <c r="L85" s="181" t="n">
-        <v>58.3606902190549</v>
+        <v>60.66869958931642</v>
       </c>
       <c r="M85" s="182" t="n">
-        <v>16961865.84679231</v>
+        <v>17265197.1038465</v>
       </c>
       <c r="N85" s="183" t="n">
-        <v>20437024.48889532</v>
+        <v>20854032.5223105</v>
       </c>
       <c r="O85" s="183" t="n">
-        <v>23359511.54972074</v>
+        <v>23999178.18703665</v>
       </c>
       <c r="P85" s="183" t="n">
-        <v>27470864.81751841</v>
+        <v>28418736.14782538</v>
       </c>
       <c r="Q85" s="184" t="n">
-        <v>31044931.43005596</v>
+        <v>32272675.52236796</v>
       </c>
       <c r="S85" s="51" t="inlineStr">
         <is>
@@ -8922,49 +8922,49 @@
         </is>
       </c>
       <c r="T85" s="185" t="n">
-        <v>485.5030309315443</v>
+        <v>494.1853448943053</v>
       </c>
       <c r="U85" s="186" t="n">
-        <v>544.9593589534441</v>
+        <v>556.0790026516669</v>
       </c>
       <c r="V85" s="186" t="n">
-        <v>597.8583593976583</v>
+        <v>614.2298509647275</v>
       </c>
       <c r="W85" s="186" t="n">
-        <v>658.3738203647393</v>
+        <v>681.0907487575593</v>
       </c>
       <c r="X85" s="187" t="n">
-        <v>713.6886244901154</v>
+        <v>741.9131027577563</v>
       </c>
       <c r="Y85" s="185" t="n">
-        <v>39.03641574691968</v>
+        <v>39.73450905613202</v>
       </c>
       <c r="Z85" s="186" t="n">
-        <v>45.76680052004829</v>
+        <v>46.70065091940266</v>
       </c>
       <c r="AA85" s="186" t="n">
-        <v>51.3778861814661</v>
+        <v>52.78479572305243</v>
       </c>
       <c r="AB85" s="186" t="n">
-        <v>59.85413421618062</v>
+        <v>61.91937745481659</v>
       </c>
       <c r="AC85" s="187" t="n">
-        <v>66.87436403579055</v>
+        <v>69.51906645869798</v>
       </c>
       <c r="AD85" s="188" t="n">
-        <v>16961865.84679231</v>
+        <v>17265197.1038465</v>
       </c>
       <c r="AE85" s="189" t="n">
-        <v>20437024.48889532</v>
+        <v>20854032.5223105</v>
       </c>
       <c r="AF85" s="189" t="n">
-        <v>23359511.54972074</v>
+        <v>23999178.18703665</v>
       </c>
       <c r="AG85" s="189" t="n">
-        <v>27470864.81751841</v>
+        <v>28418736.14782538</v>
       </c>
       <c r="AH85" s="190" t="n">
-        <v>31044931.43005596</v>
+        <v>32272675.52236796</v>
       </c>
     </row>
     <row r="86" ht="15" customHeight="1" thickBot="1"/>
@@ -9871,7 +9871,7 @@
         <v>498.9628260819919</v>
       </c>
       <c r="D95" s="80" t="n">
-        <v>531.9763172223447</v>
+        <v>531.9763172223448</v>
       </c>
       <c r="E95" s="80" t="n">
         <v>556.6558094887075</v>
@@ -9901,7 +9901,7 @@
         <v>500.8358548119919</v>
       </c>
       <c r="N95" s="80" t="n">
-        <v>534.3942127823448</v>
+        <v>534.3942127823449</v>
       </c>
       <c r="O95" s="80" t="n">
         <v>598.3903586987075</v>
@@ -9921,7 +9921,7 @@
         <v>610.469045192144</v>
       </c>
       <c r="U95" s="80" t="n">
-        <v>650.8602594498545</v>
+        <v>650.8602594498547</v>
       </c>
       <c r="V95" s="80" t="n">
         <v>681.0550260579738</v>
@@ -9951,7 +9951,7 @@
         <v>612.342073922144</v>
       </c>
       <c r="AE95" s="80" t="n">
-        <v>653.2781550098546</v>
+        <v>653.2781550098547</v>
       </c>
       <c r="AF95" s="80" t="n">
         <v>722.7895752679738</v>
